--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-observationresultslaboratorypathology.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-observationresultslaboratorypathology.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2031" uniqueCount="452">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2070" uniqueCount="459">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-10T14:16:19+00:00</t>
+    <t>2025-02-13T08:25:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -606,32 +606,55 @@
     <t>Observation.category</t>
   </si>
   <si>
+    <t xml:space="preserve">CodeableConcept {http://hl7.org/fhir/uv/ips/StructureDefinition/CodeableConcept-uv-ips}
+</t>
+  </si>
+  <si>
+    <t>Classification of  type of observation</t>
+  </si>
+  <si>
+    <t>A code that classifies the general type of observation being made.</t>
+  </si>
+  <si>
+    <t>In addition to the required category valueset, this element allows various categorization schemes based on the owner’s definition of the category and effectively multiple categories can be used at once.  The level of granularity is defined by the category concepts in the value set.</t>
+  </si>
+  <si>
+    <t>Used for filtering what observations are retrieved and displayed.</t>
+  </si>
+  <si>
+    <t>Codes for high level observation categories.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pattern:$this}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>Observation.category:laborstruktur</t>
+  </si>
+  <si>
+    <t>laborstruktur</t>
+  </si>
+  <si>
     <t xml:space="preserve">CodeableConcept
 </t>
   </si>
   <si>
-    <t>Classification of  type of observation</t>
-  </si>
-  <si>
-    <t>A code that classifies the general type of observation being made.</t>
-  </si>
-  <si>
-    <t>In addition to the required category valueset, this element allows various categorization schemes based on the owner’s definition of the category and effectively multiple categories can be used at once.  The level of granularity is defined by the category concepts in the value set.</t>
-  </si>
-  <si>
-    <t>Used for filtering what observations are retrieved and displayed.</t>
-  </si>
-  <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>https://fhir.hl7.at/elga-austrianpatientsummary-r4/ValueSet/at-aps-laboratory-pathology-category</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
+    <t>The way of grouping of the test results into clinically meaningful domains (e.g. hematology study, microbiology study, etc.)</t>
+  </si>
+  <si>
+    <t>https://termgit.elga.gv.at/ValueSet/elga-laborstruktur</t>
   </si>
   <si>
     <t>Observation.code</t>
@@ -653,7 +676,7 @@
     <t>Knowing what kind of observation is being made is essential to understanding the observation.</t>
   </si>
   <si>
-    <t>https://fhir.hl7.at/elga-austrianpatientsummary-r4/ValueSet/at-aps-laboratory-pathology-codes</t>
+    <t>https://termgit.elga.gv.at/ValueSet/elga-laborparameter</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -870,9 +893,6 @@
 </t>
   </si>
   <si>
-    <t>open</t>
-  </si>
-  <si>
     <t xml:space="preserve">obs-7
 </t>
   </si>
@@ -909,6 +929,9 @@
   </si>
   <si>
     <t>For many results it is necessary to handle exceptional values in measurements.</t>
+  </si>
+  <si>
+    <t>extensible</t>
   </si>
   <si>
     <t>Codes specifying why the result (`Observation.value[x]`) is missing.</t>
@@ -1729,7 +1752,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP52"/>
+  <dimension ref="A1:AP53"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="44.67578125" customWidth="true" bestFit="true"/>
@@ -1757,7 +1780,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="63.70703125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="90.8984375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="61.6796875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
@@ -3478,7 +3501,7 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G15" t="s" s="2">
         <v>81</v>
@@ -3530,9 +3553,11 @@
         <v>82</v>
       </c>
       <c r="X15" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="Y15" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="Y15" s="2"/>
       <c r="Z15" t="s" s="2">
         <v>196</v>
       </c>
@@ -3540,16 +3565,14 @@
         <v>82</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="AC15" s="2"/>
       <c r="AD15" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>82</v>
+        <v>198</v>
       </c>
       <c r="AF15" t="s" s="2">
         <v>189</v>
@@ -3576,10 +3599,10 @@
         <v>82</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>82</v>
@@ -3587,21 +3610,23 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="C16" s="2"/>
+        <v>189</v>
+      </c>
+      <c r="C16" t="s" s="2">
+        <v>202</v>
+      </c>
       <c r="D16" t="s" s="2">
-        <v>200</v>
+        <v>82</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
         <v>92</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>82</v>
@@ -3610,22 +3635,22 @@
         <v>82</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>82</v>
@@ -3650,7 +3675,7 @@
         <v>82</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
@@ -3672,13 +3697,13 @@
         <v>82</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>82</v>
@@ -3687,38 +3712,38 @@
         <v>104</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>206</v>
+        <v>82</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>207</v>
+        <v>82</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>208</v>
+        <v>82</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>211</v>
+        <v>82</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>82</v>
+        <v>207</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>92</v>
@@ -3733,19 +3758,19 @@
         <v>93</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>213</v>
+        <v>190</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>82</v>
@@ -3770,13 +3795,11 @@
         <v>82</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y17" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="Y17" s="2"/>
       <c r="Z17" t="s" s="2">
-        <v>82</v>
+        <v>212</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>82</v>
@@ -3794,10 +3817,10 @@
         <v>82</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="AH17" t="s" s="2">
         <v>92</v>
@@ -3809,30 +3832,30 @@
         <v>104</v>
       </c>
       <c r="AK17" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AL17" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AM17" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="AN17" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="AO17" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="AP17" t="s" s="2">
         <v>218</v>
-      </c>
-      <c r="AL17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM17" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="AN17" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="AO17" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="AP17" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3843,7 +3866,7 @@
         <v>80</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>82</v>
@@ -3855,18 +3878,20 @@
         <v>93</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="L18" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="M18" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="N18" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="O18" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="M18" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>82</v>
       </c>
@@ -3914,13 +3939,13 @@
         <v>82</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>82</v>
@@ -3929,19 +3954,19 @@
         <v>104</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>82</v>
+        <v>225</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>208</v>
+        <v>226</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>227</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>82</v>
@@ -3949,21 +3974,21 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>229</v>
+        <v>82</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>82</v>
@@ -3986,9 +4011,7 @@
       <c r="N19" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="O19" t="s" s="2">
-        <v>234</v>
-      </c>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>82</v>
       </c>
@@ -4036,13 +4059,13 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>82</v>
@@ -4051,19 +4074,19 @@
         <v>104</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>235</v>
+        <v>82</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>236</v>
+        <v>215</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>82</v>
@@ -4071,14 +4094,14 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4097,19 +4120,19 @@
         <v>93</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="M20" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="O20" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="L20" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>245</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>82</v>
@@ -4158,7 +4181,7 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4173,19 +4196,19 @@
         <v>104</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>82</v>
@@ -4193,14 +4216,14 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>82</v>
+        <v>247</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4219,18 +4242,20 @@
         <v>93</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="M21" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="N21" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="O21" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="M21" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>82</v>
       </c>
@@ -4278,7 +4303,7 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4293,19 +4318,19 @@
         <v>104</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>82</v>
+        <v>253</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM21" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="AN21" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="AN21" t="s" s="2">
+      <c r="AO21" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="AO21" t="s" s="2">
-        <v>257</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>82</v>
@@ -4313,10 +4338,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4327,7 +4352,7 @@
         <v>80</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>82</v>
@@ -4339,18 +4364,18 @@
         <v>93</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="M22" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="N22" s="2"/>
-      <c r="O22" t="s" s="2">
-        <v>262</v>
-      </c>
+      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>82</v>
       </c>
@@ -4398,13 +4423,13 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>82</v>
@@ -4413,19 +4438,19 @@
         <v>104</v>
       </c>
       <c r="AK22" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL22" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM22" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="AN22" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="AL22" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM22" t="s" s="2">
+      <c r="AO22" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="AN22" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="AO22" t="s" s="2">
-        <v>266</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>82</v>
@@ -4433,10 +4458,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4447,7 +4472,7 @@
         <v>80</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>82</v>
@@ -4459,19 +4484,17 @@
         <v>93</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="L23" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="N23" s="2"/>
+      <c r="O23" t="s" s="2">
         <v>269</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>272</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>82</v>
@@ -4508,59 +4531,59 @@
         <v>82</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="AC23" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC23" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>274</v>
+        <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>275</v>
+        <v>82</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>104</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>82</v>
+        <v>270</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>276</v>
+        <v>82</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>82</v>
+        <v>273</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>279</v>
+        <v>82</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="C24" t="s" s="2">
-        <v>281</v>
-      </c>
+        <v>274</v>
+      </c>
+      <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
         <v>82</v>
       </c>
@@ -4581,19 +4604,19 @@
         <v>93</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>190</v>
+        <v>275</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>82</v>
@@ -4618,9 +4641,11 @@
         <v>82</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="Y24" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y24" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z24" t="s" s="2">
         <v>82</v>
       </c>
@@ -4628,19 +4653,17 @@
         <v>82</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC24" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>280</v>
+      </c>
+      <c r="AC24" s="2"/>
       <c r="AD24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>82</v>
+        <v>198</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4649,7 +4672,7 @@
         <v>92</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>104</v>
@@ -4658,29 +4681,31 @@
         <v>82</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>279</v>
+        <v>285</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="C25" s="2"/>
+        <v>274</v>
+      </c>
+      <c r="C25" t="s" s="2">
+        <v>287</v>
+      </c>
       <c r="D25" t="s" s="2">
         <v>82</v>
       </c>
@@ -4698,22 +4723,22 @@
         <v>82</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>82</v>
@@ -4738,13 +4763,11 @@
         <v>82</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="Y25" t="s" s="2">
-        <v>287</v>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>288</v>
+        <v>82</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>82</v>
@@ -4762,7 +4785,7 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4771,7 +4794,7 @@
         <v>92</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>104</v>
@@ -4780,38 +4803,38 @@
         <v>82</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>82</v>
+        <v>282</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>135</v>
+        <v>283</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>82</v>
+        <v>285</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>292</v>
+        <v>82</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>82</v>
@@ -4823,19 +4846,19 @@
         <v>82</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
@@ -4860,11 +4883,13 @@
         <v>82</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="Y26" s="2"/>
+        <v>293</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>294</v>
+      </c>
       <c r="Z26" t="s" s="2">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>82</v>
@@ -4882,16 +4907,16 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>82</v>
+        <v>296</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>104</v>
@@ -4900,31 +4925,31 @@
         <v>82</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>298</v>
+        <v>82</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>299</v>
+        <v>135</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>301</v>
+        <v>82</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>82</v>
+        <v>299</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4943,19 +4968,19 @@
         <v>82</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="O27" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="L27" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>82</v>
@@ -4980,13 +5005,11 @@
         <v>82</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y27" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>293</v>
+      </c>
+      <c r="Y27" s="2"/>
       <c r="Z27" t="s" s="2">
-        <v>82</v>
+        <v>304</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>82</v>
@@ -5004,7 +5027,7 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5022,27 +5045,27 @@
         <v>82</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>82</v>
+        <v>305</v>
       </c>
       <c r="AM27" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="AN27" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="AO27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP27" t="s" s="2">
         <v>308</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="AO27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP27" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5053,7 +5076,7 @@
         <v>80</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>82</v>
@@ -5065,7 +5088,7 @@
         <v>82</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>190</v>
+        <v>310</v>
       </c>
       <c r="L28" t="s" s="2">
         <v>311</v>
@@ -5076,7 +5099,9 @@
       <c r="N28" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="O28" s="2"/>
+      <c r="O28" t="s" s="2">
+        <v>314</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>82</v>
       </c>
@@ -5100,13 +5125,13 @@
         <v>82</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>314</v>
+        <v>82</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>315</v>
+        <v>82</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>316</v>
+        <v>82</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>82</v>
@@ -5124,13 +5149,13 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>82</v>
@@ -5142,27 +5167,27 @@
         <v>82</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>317</v>
+        <v>82</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>320</v>
+        <v>82</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5185,20 +5210,18 @@
         <v>82</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>325</v>
-      </c>
+        <v>320</v>
+      </c>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>82</v>
       </c>
@@ -5222,13 +5245,13 @@
         <v>82</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>82</v>
@@ -5246,7 +5269,7 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5264,27 +5287,27 @@
         <v>82</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>82</v>
+        <v>324</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>82</v>
+        <v>327</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5307,18 +5330,20 @@
         <v>82</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="N30" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="O30" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="M30" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>82</v>
       </c>
@@ -5342,13 +5367,13 @@
         <v>82</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>82</v>
+        <v>321</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>82</v>
+        <v>333</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>82</v>
+        <v>334</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>82</v>
@@ -5366,7 +5391,7 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5384,27 +5409,27 @@
         <v>82</v>
       </c>
       <c r="AL30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM30" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="AM30" t="s" s="2">
+      <c r="AN30" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="AN30" t="s" s="2">
-        <v>337</v>
-      </c>
       <c r="AO30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>338</v>
+        <v>82</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5427,16 +5452,16 @@
         <v>82</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>343</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5486,7 +5511,7 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5504,27 +5529,27 @@
         <v>82</v>
       </c>
       <c r="AL31" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="AM31" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="AN31" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="AM31" t="s" s="2">
+      <c r="AO31" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP31" t="s" s="2">
         <v>345</v>
-      </c>
-      <c r="AN31" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="AO31" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP31" t="s" s="2">
-        <v>347</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5535,7 +5560,7 @@
         <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>82</v>
@@ -5547,20 +5572,18 @@
         <v>82</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="M32" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>353</v>
-      </c>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>82</v>
       </c>
@@ -5608,45 +5631,45 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ32" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="AM32" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="AN32" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="AO32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP32" t="s" s="2">
         <v>354</v>
-      </c>
-      <c r="AK32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="AO32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP32" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5657,7 +5680,7 @@
         <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>82</v>
@@ -5669,16 +5692,20 @@
         <v>82</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="O33" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="N33" s="2"/>
-      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>82</v>
       </c>
@@ -5726,20 +5753,20 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AG33" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH33" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ33" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="AG33" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH33" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ33" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AK33" t="s" s="2">
         <v>82</v>
       </c>
@@ -5747,10 +5774,10 @@
         <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>82</v>
+        <v>362</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>82</v>
@@ -5761,21 +5788,21 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>137</v>
+        <v>82</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>82</v>
@@ -5787,17 +5814,15 @@
         <v>82</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>138</v>
+        <v>365</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>139</v>
+        <v>366</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>141</v>
-      </c>
+        <v>367</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>82</v>
@@ -5846,19 +5871,19 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>143</v>
+        <v>82</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>82</v>
@@ -5870,7 +5895,7 @@
         <v>82</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>82</v>
@@ -5881,14 +5906,14 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>367</v>
+        <v>137</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5901,26 +5926,24 @@
         <v>82</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K35" t="s" s="2">
         <v>138</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>368</v>
+        <v>139</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="N35" t="s" s="2">
         <v>141</v>
       </c>
-      <c r="O35" t="s" s="2">
-        <v>147</v>
-      </c>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>82</v>
       </c>
@@ -5968,7 +5991,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -5992,7 +6015,7 @@
         <v>82</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>135</v>
+        <v>369</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>82</v>
@@ -6003,42 +6026,46 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>82</v>
+        <v>374</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>372</v>
+        <v>138</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="N36" s="2"/>
-      <c r="O36" s="2"/>
+        <v>376</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="O36" t="s" s="2">
+        <v>147</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>82</v>
       </c>
@@ -6086,19 +6113,19 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>375</v>
+        <v>82</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>82</v>
@@ -6107,10 +6134,10 @@
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>376</v>
+        <v>82</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>377</v>
+        <v>135</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>82</v>
@@ -6147,13 +6174,13 @@
         <v>82</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6213,7 +6240,7 @@
         <v>92</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>104</v>
@@ -6225,10 +6252,10 @@
         <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>82</v>
@@ -6239,10 +6266,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6265,20 +6292,16 @@
         <v>82</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>190</v>
+        <v>379</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>386</v>
-      </c>
+        <v>387</v>
+      </c>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>82</v>
       </c>
@@ -6302,13 +6325,13 @@
         <v>82</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>387</v>
+        <v>82</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>388</v>
+        <v>82</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>82</v>
@@ -6326,7 +6349,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6335,7 +6358,7 @@
         <v>92</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>82</v>
+        <v>382</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>104</v>
@@ -6344,13 +6367,13 @@
         <v>82</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>389</v>
+        <v>82</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>300</v>
+        <v>388</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>82</v>
@@ -6361,10 +6384,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6375,7 +6398,7 @@
         <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>82</v>
@@ -6387,19 +6410,19 @@
         <v>82</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="N39" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>395</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -6424,13 +6447,13 @@
         <v>82</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>314</v>
+        <v>116</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>82</v>
@@ -6448,13 +6471,13 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>82</v>
@@ -6466,13 +6489,13 @@
         <v>82</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -6497,7 +6520,7 @@
         <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>82</v>
@@ -6509,15 +6532,17 @@
         <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="M40" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="N40" s="2"/>
       <c r="O40" t="s" s="2">
         <v>402</v>
       </c>
@@ -6544,13 +6569,13 @@
         <v>82</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>82</v>
+        <v>321</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>82</v>
+        <v>403</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>82</v>
+        <v>404</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>82</v>
@@ -6574,7 +6599,7 @@
         <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>82</v>
@@ -6586,13 +6611,13 @@
         <v>82</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>82</v>
+        <v>396</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>82</v>
+        <v>397</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>403</v>
+        <v>307</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
@@ -6603,10 +6628,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6629,16 +6654,18 @@
         <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>358</v>
+        <v>406</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="N41" s="2"/>
-      <c r="O41" s="2"/>
+      <c r="O41" t="s" s="2">
+        <v>409</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>82</v>
       </c>
@@ -6686,7 +6713,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6707,10 +6734,10 @@
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>376</v>
+        <v>82</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -6721,10 +6748,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6735,7 +6762,7 @@
         <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>82</v>
@@ -6744,20 +6771,18 @@
         <v>82</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>409</v>
+        <v>365</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>412</v>
-      </c>
+        <v>413</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>82</v>
@@ -6806,13 +6831,13 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>82</v>
@@ -6827,7 +6852,7 @@
         <v>82</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>413</v>
+        <v>383</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>414</v>
@@ -6947,10 +6972,10 @@
         <v>82</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -6961,10 +6986,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6987,20 +7012,18 @@
         <v>93</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>349</v>
+        <v>423</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>425</v>
-      </c>
+        <v>426</v>
+      </c>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>82</v>
       </c>
@@ -7048,7 +7071,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7069,7 +7092,7 @@
         <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>427</v>
@@ -7097,7 +7120,7 @@
         <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>82</v>
@@ -7106,19 +7129,23 @@
         <v>82</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>359</v>
+        <v>429</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="N45" s="2"/>
-      <c r="O45" s="2"/>
+        <v>430</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>432</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>82</v>
       </c>
@@ -7166,19 +7193,19 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>361</v>
+        <v>428</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>82</v>
@@ -7187,10 +7214,10 @@
         <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>82</v>
+        <v>433</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>362</v>
+        <v>434</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>82</v>
@@ -7201,21 +7228,21 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>137</v>
+        <v>82</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>82</v>
@@ -7227,17 +7254,15 @@
         <v>82</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>138</v>
+        <v>365</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>139</v>
+        <v>366</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>141</v>
-      </c>
+        <v>367</v>
+      </c>
+      <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>82</v>
@@ -7286,19 +7311,19 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>143</v>
+        <v>82</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>82</v>
@@ -7310,7 +7335,7 @@
         <v>82</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>82</v>
@@ -7321,14 +7346,14 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>367</v>
+        <v>137</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7341,26 +7366,24 @@
         <v>82</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K47" t="s" s="2">
         <v>138</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>368</v>
+        <v>139</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="N47" t="s" s="2">
         <v>141</v>
       </c>
-      <c r="O47" t="s" s="2">
-        <v>147</v>
-      </c>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>82</v>
       </c>
@@ -7408,7 +7431,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7432,7 +7455,7 @@
         <v>82</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>135</v>
+        <v>369</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>82</v>
@@ -7443,45 +7466,45 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>82</v>
+        <v>374</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="J48" t="s" s="2">
         <v>93</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>190</v>
+        <v>138</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>432</v>
+        <v>375</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>433</v>
+        <v>376</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>434</v>
+        <v>141</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>204</v>
+        <v>147</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
@@ -7506,13 +7529,13 @@
         <v>82</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>314</v>
+        <v>82</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>435</v>
+        <v>82</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>436</v>
+        <v>82</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>82</v>
@@ -7530,34 +7553,34 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>431</v>
+        <v>377</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>437</v>
+        <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>208</v>
+        <v>82</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>209</v>
+        <v>135</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>210</v>
+        <v>82</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>82</v>
@@ -7576,7 +7599,7 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>92</v>
@@ -7591,19 +7614,19 @@
         <v>93</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>268</v>
+        <v>203</v>
       </c>
       <c r="L49" t="s" s="2">
         <v>439</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>270</v>
+        <v>440</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>272</v>
+        <v>211</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -7628,13 +7651,13 @@
         <v>82</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>82</v>
+        <v>321</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>82</v>
+        <v>442</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>82</v>
+        <v>443</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>82</v>
@@ -7655,7 +7678,7 @@
         <v>438</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="AH49" t="s" s="2">
         <v>92</v>
@@ -7670,27 +7693,27 @@
         <v>82</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>277</v>
+        <v>215</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>278</v>
+        <v>216</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>82</v>
+        <v>217</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>279</v>
+        <v>82</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7710,22 +7733,22 @@
         <v>82</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>190</v>
+        <v>275</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>444</v>
+        <v>277</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -7750,13 +7773,13 @@
         <v>82</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>195</v>
+        <v>82</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>287</v>
+        <v>82</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>288</v>
+        <v>82</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>82</v>
@@ -7774,7 +7797,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7783,7 +7806,7 @@
         <v>92</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>289</v>
+        <v>82</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>104</v>
@@ -7792,38 +7815,38 @@
         <v>82</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>82</v>
+        <v>448</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>135</v>
+        <v>283</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>82</v>
+        <v>285</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>292</v>
+        <v>82</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>82</v>
@@ -7835,19 +7858,19 @@
         <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>293</v>
+        <v>450</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>294</v>
+        <v>451</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>295</v>
+        <v>452</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -7872,13 +7895,13 @@
         <v>82</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>195</v>
+        <v>293</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>447</v>
+        <v>294</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>448</v>
+        <v>295</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>82</v>
@@ -7896,16 +7919,16 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>82</v>
+        <v>296</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>104</v>
@@ -7914,31 +7937,31 @@
         <v>82</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>298</v>
+        <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>299</v>
+        <v>135</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>301</v>
+        <v>82</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>82</v>
+        <v>299</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7957,19 +7980,19 @@
         <v>82</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>83</v>
+        <v>203</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>450</v>
+        <v>300</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>451</v>
+        <v>301</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>352</v>
+        <v>302</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>353</v>
+        <v>303</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
@@ -7994,13 +8017,13 @@
         <v>82</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>82</v>
+        <v>293</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>82</v>
+        <v>454</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>82</v>
+        <v>455</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>82</v>
@@ -8018,7 +8041,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8036,18 +8059,140 @@
         <v>82</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>82</v>
+        <v>305</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>355</v>
+        <v>306</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>356</v>
+        <v>307</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP52" t="s" s="2">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E53" s="2"/>
+      <c r="F53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K53" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="P53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q53" s="2"/>
+      <c r="R53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF53" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="AG53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="AN53" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="AO53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP53" t="s" s="2">
         <v>82</v>
       </c>
     </row>

--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-observationresultslaboratorypathology.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-observationresultslaboratorypathology.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T08:25:30+00:00</t>
+    <t>2025-02-13T08:54:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-observationresultslaboratorypathology.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-observationresultslaboratorypathology.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2070" uniqueCount="459">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2070" uniqueCount="460">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T08:54:32+00:00</t>
+    <t>2025-02-14T08:32:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -676,6 +676,9 @@
     <t>Knowing what kind of observation is being made is essential to understanding the observation.</t>
   </si>
   <si>
+    <t>extensible</t>
+  </si>
+  <si>
     <t>https://termgit.elga.gv.at/ValueSet/elga-laborparameter</t>
   </si>
   <si>
@@ -915,6 +918,9 @@
     <t>valueCodeableConcept</t>
   </si>
   <si>
+    <t>http://hl7.org/fhir/uv/ips/ValueSet/results-coded-values-laboratory-pathology-uv-ips</t>
+  </si>
+  <si>
     <t>Observation.dataAbsentReason</t>
   </si>
   <si>
@@ -929,9 +935,6 @@
   </si>
   <si>
     <t>For many results it is necessary to handle exceptional values in measurements.</t>
-  </si>
-  <si>
-    <t>extensible</t>
   </si>
   <si>
     <t>Codes specifying why the result (`Observation.value[x]`) is missing.</t>
@@ -1780,7 +1783,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="63.70703125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="61.6796875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="77.55859375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
@@ -3795,11 +3798,11 @@
         <v>82</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>116</v>
+        <v>212</v>
       </c>
       <c r="Y17" s="2"/>
       <c r="Z17" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>82</v>
@@ -3832,30 +3835,30 @@
         <v>104</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3878,19 +3881,19 @@
         <v>93</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>82</v>
@@ -3939,7 +3942,7 @@
         <v>82</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -3954,19 +3957,19 @@
         <v>104</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>82</v>
@@ -3974,10 +3977,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4000,16 +4003,16 @@
         <v>93</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -4059,7 +4062,7 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4080,13 +4083,13 @@
         <v>82</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>82</v>
@@ -4094,14 +4097,14 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4120,19 +4123,19 @@
         <v>93</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>82</v>
@@ -4181,7 +4184,7 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4196,19 +4199,19 @@
         <v>104</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>82</v>
@@ -4216,14 +4219,14 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4242,19 +4245,19 @@
         <v>93</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>82</v>
@@ -4303,7 +4306,7 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4318,19 +4321,19 @@
         <v>104</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>82</v>
@@ -4338,10 +4341,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4364,16 +4367,16 @@
         <v>93</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4423,7 +4426,7 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4444,13 +4447,13 @@
         <v>82</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>82</v>
@@ -4458,10 +4461,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4484,17 +4487,17 @@
         <v>93</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>82</v>
@@ -4543,7 +4546,7 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4558,19 +4561,19 @@
         <v>104</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>82</v>
@@ -4578,10 +4581,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4604,19 +4607,19 @@
         <v>93</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>82</v>
@@ -4653,7 +4656,7 @@
         <v>82</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AC24" s="2"/>
       <c r="AD24" t="s" s="2">
@@ -4663,7 +4666,7 @@
         <v>198</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4672,7 +4675,7 @@
         <v>92</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>104</v>
@@ -4681,30 +4684,30 @@
         <v>82</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D25" t="s" s="2">
         <v>82</v>
@@ -4729,16 +4732,16 @@
         <v>203</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>82</v>
@@ -4763,11 +4766,11 @@
         <v>82</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>82</v>
+        <v>212</v>
       </c>
       <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>82</v>
+        <v>289</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>82</v>
@@ -4785,7 +4788,7 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4794,7 +4797,7 @@
         <v>92</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>104</v>
@@ -4803,27 +4806,27 @@
         <v>82</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4849,16 +4852,16 @@
         <v>203</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
@@ -4883,13 +4886,13 @@
         <v>82</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>293</v>
+        <v>212</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>82</v>
@@ -4907,7 +4910,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4916,7 +4919,7 @@
         <v>92</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>104</v>
@@ -4931,7 +4934,7 @@
         <v>135</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>82</v>
@@ -4942,14 +4945,14 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4971,16 +4974,16 @@
         <v>203</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>82</v>
@@ -5005,11 +5008,11 @@
         <v>82</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>293</v>
+        <v>212</v>
       </c>
       <c r="Y27" s="2"/>
       <c r="Z27" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>82</v>
@@ -5027,7 +5030,7 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5045,27 +5048,27 @@
         <v>82</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5088,19 +5091,19 @@
         <v>82</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>82</v>
@@ -5149,7 +5152,7 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5170,10 +5173,10 @@
         <v>82</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>82</v>
@@ -5184,10 +5187,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5213,13 +5216,13 @@
         <v>203</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5245,13 +5248,13 @@
         <v>82</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>82</v>
@@ -5269,7 +5272,7 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5287,27 +5290,27 @@
         <v>82</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5333,16 +5336,16 @@
         <v>203</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>82</v>
@@ -5367,13 +5370,13 @@
         <v>82</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>82</v>
@@ -5391,7 +5394,7 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5412,10 +5415,10 @@
         <v>82</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>82</v>
@@ -5426,10 +5429,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5452,16 +5455,16 @@
         <v>82</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5511,7 +5514,7 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5529,27 +5532,27 @@
         <v>82</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5572,16 +5575,16 @@
         <v>82</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5631,7 +5634,7 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5649,27 +5652,27 @@
         <v>82</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5692,19 +5695,19 @@
         <v>82</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>82</v>
@@ -5753,7 +5756,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5765,7 +5768,7 @@
         <v>82</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>82</v>
@@ -5774,10 +5777,10 @@
         <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>82</v>
@@ -5788,10 +5791,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5814,13 +5817,13 @@
         <v>82</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5871,7 +5874,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -5895,7 +5898,7 @@
         <v>82</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>82</v>
@@ -5906,10 +5909,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5938,7 +5941,7 @@
         <v>139</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="N35" t="s" s="2">
         <v>141</v>
@@ -5991,7 +5994,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6015,7 +6018,7 @@
         <v>82</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>82</v>
@@ -6026,14 +6029,14 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -6055,10 +6058,10 @@
         <v>138</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N36" t="s" s="2">
         <v>141</v>
@@ -6113,7 +6116,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6148,10 +6151,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6174,13 +6177,13 @@
         <v>82</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6231,7 +6234,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6240,7 +6243,7 @@
         <v>92</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>104</v>
@@ -6252,10 +6255,10 @@
         <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>82</v>
@@ -6266,10 +6269,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6292,13 +6295,13 @@
         <v>82</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6349,7 +6352,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6358,7 +6361,7 @@
         <v>92</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>104</v>
@@ -6370,10 +6373,10 @@
         <v>82</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>82</v>
@@ -6384,10 +6387,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6413,16 +6416,16 @@
         <v>203</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -6450,10 +6453,10 @@
         <v>116</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>82</v>
@@ -6471,7 +6474,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6489,13 +6492,13 @@
         <v>82</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -6506,10 +6509,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6535,16 +6538,16 @@
         <v>203</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>82</v>
@@ -6569,13 +6572,13 @@
         <v>82</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>82</v>
@@ -6593,7 +6596,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6611,13 +6614,13 @@
         <v>82</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
@@ -6628,10 +6631,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6654,17 +6657,17 @@
         <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>82</v>
@@ -6713,7 +6716,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6737,7 +6740,7 @@
         <v>82</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -6748,10 +6751,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6774,13 +6777,13 @@
         <v>82</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6831,7 +6834,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6852,10 +6855,10 @@
         <v>82</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
@@ -6866,10 +6869,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6892,16 +6895,16 @@
         <v>93</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6951,7 +6954,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -6972,10 +6975,10 @@
         <v>82</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -6986,10 +6989,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7012,16 +7015,16 @@
         <v>93</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7071,7 +7074,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7092,10 +7095,10 @@
         <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
@@ -7106,10 +7109,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7132,19 +7135,19 @@
         <v>93</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>82</v>
@@ -7193,7 +7196,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7214,10 +7217,10 @@
         <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>82</v>
@@ -7228,10 +7231,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7254,13 +7257,13 @@
         <v>82</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7311,7 +7314,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7335,7 +7338,7 @@
         <v>82</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>82</v>
@@ -7346,10 +7349,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7378,7 +7381,7 @@
         <v>139</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="N47" t="s" s="2">
         <v>141</v>
@@ -7431,7 +7434,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7455,7 +7458,7 @@
         <v>82</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>82</v>
@@ -7466,14 +7469,14 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7495,10 +7498,10 @@
         <v>138</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N48" t="s" s="2">
         <v>141</v>
@@ -7553,7 +7556,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7588,10 +7591,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7617,13 +7620,13 @@
         <v>203</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="O49" t="s" s="2">
         <v>211</v>
@@ -7651,13 +7654,13 @@
         <v>82</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>82</v>
@@ -7675,7 +7678,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>92</v>
@@ -7693,16 +7696,16 @@
         <v>82</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>82</v>
@@ -7710,10 +7713,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7736,19 +7739,19 @@
         <v>93</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -7797,7 +7800,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7815,27 +7818,27 @@
         <v>82</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7861,16 +7864,16 @@
         <v>203</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -7895,13 +7898,13 @@
         <v>82</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>293</v>
+        <v>212</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>82</v>
@@ -7919,7 +7922,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -7928,7 +7931,7 @@
         <v>92</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>104</v>
@@ -7943,7 +7946,7 @@
         <v>135</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -7954,14 +7957,14 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7983,16 +7986,16 @@
         <v>203</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
@@ -8017,31 +8020,31 @@
         <v>82</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>293</v>
+        <v>212</v>
       </c>
       <c r="Y52" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF52" t="s" s="2">
         <v>454</v>
-      </c>
-      <c r="Z52" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="AA52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF52" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8059,27 +8062,27 @@
         <v>82</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8105,16 +8108,16 @@
         <v>83</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>82</v>
@@ -8163,7 +8166,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8184,10 +8187,10 @@
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>82</v>

--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-observationresultslaboratorypathology.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-observationresultslaboratorypathology.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-14T08:32:04+00:00</t>
+    <t>2025-02-14T09:49:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-observationresultslaboratorypathology.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-observationresultslaboratorypathology.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2070" uniqueCount="460">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2031" uniqueCount="454">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-14T09:49:00+00:00</t>
+    <t>2025-02-17T15:20:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -606,64 +606,45 @@
     <t>Observation.category</t>
   </si>
   <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>Classification of  type of observation</t>
+  </si>
+  <si>
+    <t>A code that classifies the general type of observation being made.</t>
+  </si>
+  <si>
+    <t>In addition to the required category valueset, this element allows various categorization schemes based on the owner’s definition of the category and effectively multiple categories can be used at once.  The level of granularity is defined by the category concepts in the value set.</t>
+  </si>
+  <si>
+    <t>Used for filtering what observations are retrieved and displayed.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>https://termgit.elga.gv.at/ValueSet/elga-laborstruktur</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>Observation.code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name
+</t>
+  </si>
+  <si>
     <t xml:space="preserve">CodeableConcept {http://hl7.org/fhir/uv/ips/StructureDefinition/CodeableConcept-uv-ips}
 </t>
   </si>
   <si>
-    <t>Classification of  type of observation</t>
-  </si>
-  <si>
-    <t>A code that classifies the general type of observation being made.</t>
-  </si>
-  <si>
-    <t>In addition to the required category valueset, this element allows various categorization schemes based on the owner’s definition of the category and effectively multiple categories can be used at once.  The level of granularity is defined by the category concepts in the value set.</t>
-  </si>
-  <si>
-    <t>Used for filtering what observations are retrieved and displayed.</t>
-  </si>
-  <si>
-    <t>Codes for high level observation categories.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pattern:$this}
-</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>Observation.category:laborstruktur</t>
-  </si>
-  <si>
-    <t>laborstruktur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
-  </si>
-  <si>
-    <t>The way of grouping of the test results into clinically meaningful domains (e.g. hematology study, microbiology study, etc.)</t>
-  </si>
-  <si>
-    <t>https://termgit.elga.gv.at/ValueSet/elga-laborstruktur</t>
-  </si>
-  <si>
-    <t>Observation.code</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Name
-</t>
-  </si>
-  <si>
     <t>Type of observation (code / type)</t>
   </si>
   <si>
@@ -674,9 +655,6 @@
   </si>
   <si>
     <t>Knowing what kind of observation is being made is essential to understanding the observation.</t>
-  </si>
-  <si>
-    <t>extensible</t>
   </si>
   <si>
     <t>https://termgit.elga.gv.at/ValueSet/elga-laborparameter</t>
@@ -894,6 +872,9 @@
   <si>
     <t xml:space="preserve">type:$this}
 </t>
+  </si>
+  <si>
+    <t>open</t>
   </si>
   <si>
     <t xml:space="preserve">obs-7
@@ -1755,7 +1736,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP53"/>
+  <dimension ref="A1:AP52"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="44.67578125" customWidth="true" bestFit="true"/>
@@ -3504,7 +3485,7 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G15" t="s" s="2">
         <v>81</v>
@@ -3556,11 +3537,9 @@
         <v>82</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="Y15" t="s" s="2">
         <v>195</v>
       </c>
+      <c r="Y15" s="2"/>
       <c r="Z15" t="s" s="2">
         <v>196</v>
       </c>
@@ -3568,14 +3547,16 @@
         <v>82</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="AC15" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD15" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>198</v>
+        <v>82</v>
       </c>
       <c r="AF15" t="s" s="2">
         <v>189</v>
@@ -3602,10 +3583,10 @@
         <v>82</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>82</v>
@@ -3613,23 +3594,21 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="C16" t="s" s="2">
-        <v>202</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>82</v>
+        <v>200</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
         <v>92</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>82</v>
@@ -3638,22 +3617,22 @@
         <v>82</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L16" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="M16" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="M16" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>193</v>
-      </c>
       <c r="O16" t="s" s="2">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>82</v>
@@ -3678,11 +3657,11 @@
         <v>82</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>82</v>
@@ -3700,13 +3679,13 @@
         <v>82</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>82</v>
@@ -3715,38 +3694,38 @@
         <v>104</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>82</v>
+        <v>207</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>82</v>
+        <v>208</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>82</v>
+        <v>209</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>82</v>
+        <v>212</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>207</v>
+        <v>82</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>92</v>
@@ -3761,19 +3740,19 @@
         <v>93</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>190</v>
+        <v>214</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>82</v>
@@ -3798,32 +3777,34 @@
         <v>82</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="Y17" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y17" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF17" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="AA17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF17" t="s" s="2">
-        <v>206</v>
-      </c>
       <c r="AG17" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="AH17" t="s" s="2">
         <v>92</v>
@@ -3835,30 +3816,30 @@
         <v>104</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>215</v>
+        <v>82</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>219</v>
+        <v>82</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3869,7 +3850,7 @@
         <v>80</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>82</v>
@@ -3881,20 +3862,18 @@
         <v>93</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>225</v>
-      </c>
+        <v>227</v>
+      </c>
+      <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>82</v>
       </c>
@@ -3942,13 +3921,13 @@
         <v>82</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>82</v>
@@ -3957,19 +3936,19 @@
         <v>104</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>226</v>
+        <v>82</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>227</v>
+        <v>209</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>228</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>82</v>
@@ -3977,21 +3956,21 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>82</v>
+        <v>230</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>82</v>
@@ -4014,7 +3993,9 @@
       <c r="N19" t="s" s="2">
         <v>234</v>
       </c>
-      <c r="O19" s="2"/>
+      <c r="O19" t="s" s="2">
+        <v>235</v>
+      </c>
       <c r="P19" t="s" s="2">
         <v>82</v>
       </c>
@@ -4062,13 +4043,13 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>82</v>
@@ -4077,19 +4058,19 @@
         <v>104</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>82</v>
+        <v>236</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>216</v>
+        <v>237</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>82</v>
@@ -4097,14 +4078,14 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4123,19 +4104,19 @@
         <v>93</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>82</v>
@@ -4184,7 +4165,7 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4199,19 +4180,19 @@
         <v>104</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>82</v>
@@ -4219,14 +4200,14 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>248</v>
+        <v>82</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4245,20 +4226,18 @@
         <v>93</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>253</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>82</v>
       </c>
@@ -4306,7 +4285,7 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4321,19 +4300,19 @@
         <v>104</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>254</v>
+        <v>82</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>82</v>
@@ -4341,10 +4320,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4355,7 +4334,7 @@
         <v>80</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>82</v>
@@ -4367,18 +4346,18 @@
         <v>93</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="N22" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="O22" s="2"/>
+      <c r="N22" s="2"/>
+      <c r="O22" t="s" s="2">
+        <v>263</v>
+      </c>
       <c r="P22" t="s" s="2">
         <v>82</v>
       </c>
@@ -4426,13 +4405,13 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>82</v>
@@ -4441,19 +4420,19 @@
         <v>104</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>82</v>
+        <v>264</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>82</v>
@@ -4461,10 +4440,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4475,7 +4454,7 @@
         <v>80</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>82</v>
@@ -4487,17 +4466,19 @@
         <v>93</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="N23" s="2"/>
+        <v>271</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>272</v>
+      </c>
       <c r="O23" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>82</v>
@@ -4534,59 +4515,59 @@
         <v>82</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC23" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>274</v>
+      </c>
+      <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>82</v>
+        <v>275</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>82</v>
+        <v>276</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>104</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>271</v>
+        <v>82</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>82</v>
+        <v>277</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>274</v>
+        <v>82</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>82</v>
+        <v>280</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="C24" s="2"/>
+        <v>268</v>
+      </c>
+      <c r="C24" t="s" s="2">
+        <v>282</v>
+      </c>
       <c r="D24" t="s" s="2">
         <v>82</v>
       </c>
@@ -4607,19 +4588,19 @@
         <v>93</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>276</v>
+        <v>190</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>82</v>
@@ -4644,29 +4625,29 @@
         <v>82</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y24" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
-        <v>82</v>
+        <v>283</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="AC24" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>198</v>
+        <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4675,7 +4656,7 @@
         <v>92</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>104</v>
@@ -4684,31 +4665,29 @@
         <v>82</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="C25" t="s" s="2">
-        <v>288</v>
-      </c>
+        <v>284</v>
+      </c>
+      <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
         <v>82</v>
       </c>
@@ -4726,22 +4705,22 @@
         <v>82</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>82</v>
@@ -4766,11 +4745,13 @@
         <v>82</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="Y25" s="2"/>
+        <v>195</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>289</v>
+      </c>
       <c r="Z25" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>82</v>
@@ -4788,7 +4769,7 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4797,7 +4778,7 @@
         <v>92</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>104</v>
@@ -4806,38 +4787,38 @@
         <v>82</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>283</v>
+        <v>82</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>284</v>
+        <v>135</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>286</v>
+        <v>82</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>82</v>
+        <v>294</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>82</v>
@@ -4849,19 +4830,19 @@
         <v>82</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
@@ -4886,13 +4867,11 @@
         <v>82</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="Y26" t="s" s="2">
-        <v>295</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>82</v>
@@ -4910,16 +4889,16 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>297</v>
+        <v>82</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>104</v>
@@ -4928,31 +4907,31 @@
         <v>82</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>82</v>
+        <v>300</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>135</v>
+        <v>301</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>82</v>
+        <v>303</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>300</v>
+        <v>82</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4971,19 +4950,19 @@
         <v>82</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>203</v>
+        <v>305</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>82</v>
@@ -5008,11 +4987,13 @@
         <v>82</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="Y27" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z27" t="s" s="2">
-        <v>305</v>
+        <v>82</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>82</v>
@@ -5030,7 +5011,7 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5048,27 +5029,27 @@
         <v>82</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>306</v>
+        <v>82</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>309</v>
+        <v>82</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5079,7 +5060,7 @@
         <v>80</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>82</v>
@@ -5091,20 +5072,18 @@
         <v>82</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>311</v>
+        <v>190</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="O28" t="s" s="2">
         <v>315</v>
       </c>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>82</v>
       </c>
@@ -5128,13 +5107,13 @@
         <v>82</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>82</v>
+        <v>316</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>82</v>
+        <v>317</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>82</v>
+        <v>318</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>82</v>
@@ -5152,13 +5131,13 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>82</v>
@@ -5170,27 +5149,27 @@
         <v>82</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>82</v>
+        <v>319</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>82</v>
+        <v>322</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5213,18 +5192,20 @@
         <v>82</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="O29" s="2"/>
+        <v>326</v>
+      </c>
+      <c r="O29" t="s" s="2">
+        <v>327</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>82</v>
       </c>
@@ -5248,31 +5229,31 @@
         <v>82</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="Y29" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="Z29" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="AA29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF29" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="Z29" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="AA29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF29" t="s" s="2">
-        <v>318</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5290,27 +5271,27 @@
         <v>82</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>325</v>
+        <v>82</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>328</v>
+        <v>82</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5333,20 +5314,18 @@
         <v>82</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>203</v>
+        <v>333</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>333</v>
-      </c>
+        <v>336</v>
+      </c>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>82</v>
       </c>
@@ -5370,13 +5349,13 @@
         <v>82</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>322</v>
+        <v>82</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>334</v>
+        <v>82</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>335</v>
+        <v>82</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>82</v>
@@ -5394,7 +5373,7 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5412,27 +5391,27 @@
         <v>82</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>82</v>
+        <v>337</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>82</v>
+        <v>340</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5455,16 +5434,16 @@
         <v>82</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5514,7 +5493,7 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5532,27 +5511,27 @@
         <v>82</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5563,7 +5542,7 @@
         <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>82</v>
@@ -5575,18 +5554,20 @@
         <v>82</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="O32" s="2"/>
+        <v>354</v>
+      </c>
+      <c r="O32" t="s" s="2">
+        <v>355</v>
+      </c>
       <c r="P32" t="s" s="2">
         <v>82</v>
       </c>
@@ -5634,45 +5615,45 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>104</v>
+        <v>356</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>352</v>
+        <v>82</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>355</v>
+        <v>82</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5683,7 +5664,7 @@
         <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>82</v>
@@ -5695,20 +5676,16 @@
         <v>82</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>361</v>
-      </c>
+        <v>362</v>
+      </c>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>82</v>
       </c>
@@ -5756,19 +5733,19 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>362</v>
+        <v>82</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>82</v>
@@ -5777,7 +5754,7 @@
         <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>363</v>
+        <v>82</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>364</v>
@@ -5798,14 +5775,14 @@
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>82</v>
+        <v>137</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>82</v>
@@ -5817,15 +5794,17 @@
         <v>82</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="L34" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="L34" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="N34" s="2"/>
+      <c r="N34" t="s" s="2">
+        <v>141</v>
+      </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>82</v>
@@ -5874,19 +5853,19 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>82</v>
+        <v>143</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>82</v>
@@ -5898,7 +5877,7 @@
         <v>82</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>82</v>
@@ -5909,14 +5888,14 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>137</v>
+        <v>369</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5929,24 +5908,26 @@
         <v>82</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K35" t="s" s="2">
         <v>138</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>139</v>
+        <v>370</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="N35" t="s" s="2">
         <v>141</v>
       </c>
-      <c r="O35" s="2"/>
+      <c r="O35" t="s" s="2">
+        <v>147</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
       </c>
@@ -5994,7 +5975,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6018,7 +5999,7 @@
         <v>82</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>370</v>
+        <v>135</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>82</v>
@@ -6029,46 +6010,42 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>375</v>
+        <v>82</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>138</v>
+        <v>374</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="M36" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>147</v>
-      </c>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>82</v>
       </c>
@@ -6116,31 +6093,31 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="AG36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH36" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI36" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="AJ36" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM36" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="AG36" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH36" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ36" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="AK36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM36" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AN36" t="s" s="2">
-        <v>135</v>
+        <v>379</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>82</v>
@@ -6151,10 +6128,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6177,7 +6154,7 @@
         <v>82</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="L37" t="s" s="2">
         <v>381</v>
@@ -6234,7 +6211,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6243,7 +6220,7 @@
         <v>92</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>104</v>
@@ -6255,10 +6232,10 @@
         <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>82</v>
@@ -6269,10 +6246,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6295,16 +6272,20 @@
         <v>82</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>380</v>
+        <v>190</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="M38" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="N38" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="O38" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="N38" s="2"/>
-      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>82</v>
       </c>
@@ -6328,13 +6309,13 @@
         <v>82</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>82</v>
+        <v>389</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>82</v>
+        <v>390</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>82</v>
@@ -6352,7 +6333,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6361,7 +6342,7 @@
         <v>92</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>383</v>
+        <v>82</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>104</v>
@@ -6370,13 +6351,13 @@
         <v>82</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>82</v>
+        <v>391</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>389</v>
+        <v>302</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>82</v>
@@ -6387,10 +6368,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6401,7 +6382,7 @@
         <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>82</v>
@@ -6413,19 +6394,19 @@
         <v>82</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -6450,13 +6431,13 @@
         <v>82</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>116</v>
+        <v>316</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>82</v>
@@ -6474,13 +6455,13 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>82</v>
@@ -6492,13 +6473,13 @@
         <v>82</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -6509,10 +6490,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6523,7 +6504,7 @@
         <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>82</v>
@@ -6535,19 +6516,17 @@
         <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>203</v>
+        <v>401</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>402</v>
-      </c>
+        <v>403</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>82</v>
@@ -6572,13 +6551,13 @@
         <v>82</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>322</v>
+        <v>82</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>404</v>
+        <v>82</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>405</v>
+        <v>82</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>82</v>
@@ -6596,13 +6575,13 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>82</v>
@@ -6614,13 +6593,13 @@
         <v>82</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>397</v>
+        <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>398</v>
+        <v>82</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>308</v>
+        <v>405</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
@@ -6657,18 +6636,16 @@
         <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="M41" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="M41" t="s" s="2">
-        <v>409</v>
-      </c>
       <c r="N41" s="2"/>
-      <c r="O41" t="s" s="2">
-        <v>410</v>
-      </c>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>82</v>
       </c>
@@ -6737,10 +6714,10 @@
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>82</v>
+        <v>378</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -6751,10 +6728,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6765,7 +6742,7 @@
         <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>82</v>
@@ -6774,18 +6751,20 @@
         <v>82</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>366</v>
+        <v>411</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>82</v>
@@ -6834,13 +6813,13 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>82</v>
@@ -6855,10 +6834,10 @@
         <v>82</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>384</v>
+        <v>415</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
@@ -6869,10 +6848,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6895,16 +6874,16 @@
         <v>93</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6954,7 +6933,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -6975,7 +6954,7 @@
         <v>82</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>422</v>
@@ -7015,18 +6994,20 @@
         <v>93</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="L44" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="M44" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="N44" t="s" s="2">
+      <c r="O44" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>82</v>
       </c>
@@ -7095,10 +7076,10 @@
         <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
@@ -7109,10 +7090,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7123,7 +7104,7 @@
         <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>82</v>
@@ -7132,23 +7113,19 @@
         <v>82</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>430</v>
+        <v>361</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>433</v>
-      </c>
+        <v>362</v>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>82</v>
       </c>
@@ -7196,19 +7173,19 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>429</v>
+        <v>363</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>82</v>
@@ -7217,10 +7194,10 @@
         <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>434</v>
+        <v>82</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>435</v>
+        <v>364</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>82</v>
@@ -7231,21 +7208,21 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>82</v>
+        <v>137</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>82</v>
@@ -7257,15 +7234,17 @@
         <v>82</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="L46" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="N46" s="2"/>
+      <c r="N46" t="s" s="2">
+        <v>141</v>
+      </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>82</v>
@@ -7314,19 +7293,19 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>82</v>
+        <v>143</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>82</v>
@@ -7338,7 +7317,7 @@
         <v>82</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>82</v>
@@ -7349,14 +7328,14 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>137</v>
+        <v>369</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7369,24 +7348,26 @@
         <v>82</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K47" t="s" s="2">
         <v>138</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>139</v>
+        <v>370</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="N47" t="s" s="2">
         <v>141</v>
       </c>
-      <c r="O47" s="2"/>
+      <c r="O47" t="s" s="2">
+        <v>147</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>82</v>
       </c>
@@ -7434,7 +7415,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7458,7 +7439,7 @@
         <v>82</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>370</v>
+        <v>135</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>82</v>
@@ -7469,45 +7450,45 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>375</v>
+        <v>82</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="J48" t="s" s="2">
         <v>93</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>138</v>
+        <v>190</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>376</v>
+        <v>434</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>377</v>
+        <v>435</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>141</v>
+        <v>436</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>147</v>
+        <v>205</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
@@ -7532,13 +7513,13 @@
         <v>82</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>82</v>
+        <v>316</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>82</v>
+        <v>437</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>82</v>
+        <v>438</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>82</v>
@@ -7556,34 +7537,34 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>378</v>
+        <v>433</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>143</v>
+        <v>104</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>82</v>
+        <v>439</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>82</v>
+        <v>209</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>135</v>
+        <v>210</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>82</v>
+        <v>211</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>82</v>
@@ -7591,10 +7572,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7602,7 +7583,7 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>92</v>
@@ -7617,19 +7598,19 @@
         <v>93</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>203</v>
+        <v>269</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>441</v>
+        <v>271</v>
       </c>
       <c r="N49" t="s" s="2">
         <v>442</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>211</v>
+        <v>273</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -7654,13 +7635,13 @@
         <v>82</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>322</v>
+        <v>82</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>443</v>
+        <v>82</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>444</v>
+        <v>82</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>82</v>
@@ -7678,10 +7659,10 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
         <v>92</v>
@@ -7696,27 +7677,27 @@
         <v>82</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>216</v>
+        <v>278</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>217</v>
+        <v>279</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>218</v>
+        <v>82</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>82</v>
+        <v>280</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7736,22 +7717,22 @@
         <v>82</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>276</v>
+        <v>190</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="N50" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="M50" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>448</v>
-      </c>
       <c r="O50" t="s" s="2">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -7776,13 +7757,13 @@
         <v>82</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>82</v>
+        <v>195</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>82</v>
+        <v>289</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>82</v>
+        <v>290</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>82</v>
@@ -7800,7 +7781,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7809,7 +7790,7 @@
         <v>92</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>82</v>
+        <v>291</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>104</v>
@@ -7818,38 +7799,38 @@
         <v>82</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>449</v>
+        <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>284</v>
+        <v>135</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>286</v>
+        <v>82</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>82</v>
+        <v>294</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>82</v>
@@ -7861,19 +7842,19 @@
         <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>451</v>
+        <v>295</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>452</v>
+        <v>296</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>453</v>
+        <v>297</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -7898,13 +7879,13 @@
         <v>82</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>212</v>
+        <v>195</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>295</v>
+        <v>449</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>296</v>
+        <v>450</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>82</v>
@@ -7922,16 +7903,16 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>297</v>
+        <v>82</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>104</v>
@@ -7940,31 +7921,31 @@
         <v>82</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>82</v>
+        <v>300</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>135</v>
+        <v>301</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>82</v>
+        <v>303</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>300</v>
+        <v>82</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7983,19 +7964,19 @@
         <v>82</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>203</v>
+        <v>83</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>301</v>
+        <v>452</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>302</v>
+        <v>453</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>303</v>
+        <v>354</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>304</v>
+        <v>355</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
@@ -8020,13 +8001,13 @@
         <v>82</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>212</v>
+        <v>82</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>455</v>
+        <v>82</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>456</v>
+        <v>82</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>82</v>
@@ -8044,7 +8025,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8062,140 +8043,18 @@
         <v>82</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>306</v>
+        <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>307</v>
+        <v>357</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>308</v>
+        <v>358</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="B53" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="C53" s="2"/>
-      <c r="D53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E53" s="2"/>
-      <c r="F53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G53" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K53" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="L53" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="P53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q53" s="2"/>
-      <c r="R53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF53" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="AG53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH53" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ53" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM53" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="AO53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP53" t="s" s="2">
         <v>82</v>
       </c>
     </row>

--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-observationresultslaboratorypathology.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-observationresultslaboratorypathology.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-17T15:20:00+00:00</t>
+    <t>2025-02-18T09:36:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-observationresultslaboratorypathology.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-observationresultslaboratorypathology.xlsx
@@ -9,11 +9,14 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$65</definedName>
+  </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2031" uniqueCount="454">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2526" uniqueCount="503">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T09:36:51+00:00</t>
+    <t>2025-02-21T10:11:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -111,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Observation</t>
+    <t>http://hl7.org/fhir/uv/ips/StructureDefinition/Observation-results-laboratory-pathology-uv-ips</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -269,14 +272,14 @@
 </t>
   </si>
   <si>
-    <t>Measurements and simple assertions made about a patient, device or other subject.</t>
-  </si>
-  <si>
-    <t>Used for simple observations such as device measurements, laboratory atomic results, vital signs, height, weight, smoking status, comments, etc.  Other resources are used to provide context for observations such as laboratory reports, etc.</t>
+    <t>This observation may represent the result of a simple laboratory or pathology test such as hematocrit, or it may group the set of results produced by a multi-test study or panel such as a complete blood count, a dynamic function test, or a urine specimen study. In the latter case, the observation carries the overall conclusion of the study and references the atomic results of the study as "has-member" child observations</t>
+  </si>
+  <si>
+    <t>Represents either a lab simple observation or the group of observations produced by a laboratory study.</t>
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}ips-2:At least one of these Observation elements shall be provided:  "value", "dataAbsentReason", "hasMember" or "component" {value.exists() or hasMember.exists() or component.exists() or dataAbsentReason.exists()}ips-3:If observation has components, at least one of these Observation.component elements shall be provided:  "value" or "dataAbsentReason" {component.exists() implies (component.value.exists() or component.dataAbsentReason.exists())}</t>
   </si>
   <si>
     <t>Event</t>
@@ -567,6 +570,9 @@
     <t>Observation.status</t>
   </si>
   <si>
+    <t>Observation 'complete' status codes</t>
+  </si>
+  <si>
     <t>registered | preliminary | final | amended +</t>
   </si>
   <si>
@@ -582,10 +588,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>Codes providing the status of an observation.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-status|4.0.1</t>
+    <t>http://hl7.org/fhir/uv/ips/ValueSet/results-status-uv-ips</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -604,34 +607,71 @@
   </si>
   <si>
     <t>Observation.category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept {http://hl7.org/fhir/uv/ips/StructureDefinition/CodeableConcept-uv-ips}
+</t>
+  </si>
+  <si>
+    <t>Classification of  type of observation</t>
+  </si>
+  <si>
+    <t>A code that classifies the general type of observation being made. In this profile, fixed to "laboratory".</t>
+  </si>
+  <si>
+    <t>"laboratory" includes laboratory medicine and pathology</t>
+  </si>
+  <si>
+    <t>Used for filtering what observations are retrieved and displayed.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>https://termgit.elga.gv.at/ValueSet/elga-laborstruktur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pattern:$this}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>Observation.category:laboratory</t>
+  </si>
+  <si>
+    <t>laboratory</t>
   </si>
   <si>
     <t xml:space="preserve">CodeableConcept
 </t>
   </si>
   <si>
-    <t>Classification of  type of observation</t>
-  </si>
-  <si>
     <t>A code that classifies the general type of observation being made.</t>
   </si>
   <si>
     <t>In addition to the required category valueset, this element allows various categorization schemes based on the owner’s definition of the category and effectively multiple categories can be used at once.  The level of granularity is defined by the category concepts in the value set.</t>
   </si>
   <si>
-    <t>Used for filtering what observations are retrieved and displayed.</t>
-  </si>
-  <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>https://termgit.elga.gv.at/ValueSet/elga-laborstruktur</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://terminology.hl7.org/CodeSystem/observation-category"/&gt;
+    &lt;code value="laboratory"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
+    <t>Codes for high level observation categories.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
   </si>
   <si>
     <t>Observation.code</t>
@@ -641,41 +681,29 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">CodeableConcept {http://hl7.org/fhir/uv/ips/StructureDefinition/CodeableConcept-uv-ips}
+    <t>Concept - reference to a terminology or just  text</t>
+  </si>
+  <si>
+    <t>Describes what was observed. Sometimes this is called the observation "name".  In this profile this code represents either a simple laboratory test or a single pathology examination or a laboratory or pathology study with multiple child observations.</t>
+  </si>
+  <si>
+    <t>In the context of this Observation-results-laboratory-pathology-uv-ips profile, when the observation plays the role of a grouper of member sub-observations, the code represents the group (for instance a panel code). In case no code is available, at least a text shall be provided.</t>
+  </si>
+  <si>
+    <t>Knowing what kind of observation is being made is essential to understanding the observation.</t>
+  </si>
+  <si>
+    <t>https://termgit.elga.gv.at/ValueSet/elga-laborparameter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
 </t>
   </si>
   <si>
-    <t>Type of observation (code / type)</t>
-  </si>
-  <si>
-    <t>Describes what was observed. Sometimes this is called the observation "name".</t>
-  </si>
-  <si>
-    <t>*All* code-value and, if present, component.code-component.value pairs need to be taken into account to correctly understand the meaning of the observation.</t>
-  </si>
-  <si>
-    <t>Knowing what kind of observation is being made is essential to understanding the observation.</t>
-  </si>
-  <si>
-    <t>https://termgit.elga.gv.at/ValueSet/elga-laborparameter</t>
-  </si>
-  <si>
-    <t>Event.code</t>
-  </si>
-  <si>
-    <t>&lt; 363787002 |Observable entity| OR &lt; 386053000 |Evaluation procedure|</t>
-  </si>
-  <si>
-    <t>OBX-3</t>
-  </si>
-  <si>
-    <t>code</t>
-  </si>
-  <si>
-    <t>FiveWs.what[x]</t>
-  </si>
-  <si>
-    <t>116680003 |Is a|</t>
+    <t>CE/CNE/CWE</t>
+  </si>
+  <si>
+    <t>CD</t>
   </si>
   <si>
     <t>Observation.subject</t>
@@ -688,7 +716,8 @@
     <t>Who and/or what the observation is about</t>
   </si>
   <si>
-    <t>The patient, or group of patients, location, or device this observation is about and into whose record the observation is placed. If the actual focus of the observation is different from the subject (or a sample of, part, or region of the subject), the `focus` element or the `code` itself specifies the actual focus of the observation.</t>
+    <t>The patient, or group of patients, location, or device whose characteristics (direct or indirect) are described by the observation and into whose record the observation is placed.  Comments: Indirect characteristics may be those of a specimen, fetus, donor, other observer (for example a relative or EMT), or any observation made about the subject.
+In this profile is constrained to the patient</t>
   </si>
   <si>
     <t>One would expect this element to be a cardinality of 1..1. The only circumstance in which the subject can be missing is when the observation is made by a device that does not know the patient. In this case, the observation SHALL be matched to a patient through some context/channel matching technique, and at this point, the observation should be updated.</t>
@@ -707,6 +736,118 @@
   </si>
   <si>
     <t>FiveWs.subject</t>
+  </si>
+  <si>
+    <t>Observation.subject.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Observation.subject.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Observation.subject.reference</t>
+  </si>
+  <si>
+    <t>Literal reference, Relative, internal or absolute URL</t>
+  </si>
+  <si>
+    <t>A reference to a location at which the other resource is found. The reference may be a relative reference, in which case it is relative to the service base URL, or an absolute URL that resolves to the location where the resource is found. The reference may be version specific or not. If the reference is not to a FHIR RESTful server, then it should be assumed to be version specific. Internal fragment references (start with '#') refer to contained resources.</t>
+  </si>
+  <si>
+    <t>Using absolute URLs provides a stable scalable approach suitable for a cloud/web context, while using relative/logical references provides a flexible approach suitable for use when trading across closed eco-system boundaries.   Absolute URLs do not need to point to a FHIR RESTful server, though this is the preferred approach. If the URL conforms to the structure "/[type]/[id]" then it should be assumed that the reference is to a FHIR RESTful server.</t>
+  </si>
+  <si>
+    <t>Reference.reference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ref-1
+</t>
+  </si>
+  <si>
+    <t>Observation.subject.type</t>
+  </si>
+  <si>
+    <t>Type the reference refers to (e.g. "Patient")</t>
+  </si>
+  <si>
+    <t>The expected type of the target of the reference. If both Reference.type and Reference.reference are populated and Reference.reference is a FHIR URL, both SHALL be consistent.
+The type is the Canonical URL of Resource Definition that is the type this reference refers to. References are URLs that are relative to http://hl7.org/fhir/StructureDefinition/ e.g. "Patient" is a reference to http://hl7.org/fhir/StructureDefinition/Patient. Absolute URLs are only allowed for logical models (and can only be used in references in logical models, not resources).</t>
+  </si>
+  <si>
+    <t>This element is used to indicate the type of  the target of the reference. This may be used which ever of the other elements are populated (or not). In some cases, the type of the target may be determined by inspection of the reference (e.g. a RESTful URL) or by resolving the target of the reference; if both the type and a reference is provided, the reference SHALL resolve to a resource of the same type as that specified.</t>
+  </si>
+  <si>
+    <t>Aa resource (or, for logical models, the URI of the logical model).</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/resource-types</t>
+  </si>
+  <si>
+    <t>Reference.type</t>
+  </si>
+  <si>
+    <t>Observation.subject.identifier</t>
+  </si>
+  <si>
+    <t>Logical reference, when literal reference is not known</t>
+  </si>
+  <si>
+    <t>An identifier for the target resource. This is used when there is no way to reference the other resource directly, either because the entity it represents is not available through a FHIR server, or because there is no way for the author of the resource to convert a known identifier to an actual location. There is no requirement that a Reference.identifier point to something that is actually exposed as a FHIR instance, but it SHALL point to a business concept that would be expected to be exposed as a FHIR instance, and that instance would need to be of a FHIR resource type allowed by the reference.</t>
+  </si>
+  <si>
+    <t>When an identifier is provided in place of a reference, any system processing the reference will only be able to resolve the identifier to a reference if it understands the business context in which the identifier is used. Sometimes this is global (e.g. a national identifier) but often it is not. For this reason, none of the useful mechanisms described for working with references (e.g. chaining, includes) are possible, nor should servers be expected to be able resolve the reference. Servers may accept an identifier based reference untouched, resolve it, and/or reject it - see CapabilityStatement.rest.resource.referencePolicy. 
+When both an identifier and a literal reference are provided, the literal reference is preferred. Applications processing the resource are allowed - but not required - to check that the identifier matches the literal reference
+Applications converting a logical reference to a literal reference may choose to leave the logical reference present, or remove it.
+Reference is intended to point to a structure that can potentially be expressed as a FHIR resource, though there is no need for it to exist as an actual FHIR resource instance - except in as much as an application wishes to actual find the target of the reference. The content referred to be the identifier must meet the logical constraints implied by any limitations on what resource types are permitted for the reference.  For example, it would not be legitimate to send the identifier for a drug prescription if the type were Reference(Observation|DiagnosticReport).  One of the use-cases for Reference.identifier is the situation where no FHIR representation exists (where the type is Reference (Any).</t>
+  </si>
+  <si>
+    <t>Reference.identifier</t>
+  </si>
+  <si>
+    <t>.identifier</t>
+  </si>
+  <si>
+    <t>Observation.subject.display</t>
+  </si>
+  <si>
+    <t>Text alternative for the resource</t>
+  </si>
+  <si>
+    <t>Plain text narrative that identifies the resource in addition to the resource reference.</t>
+  </si>
+  <si>
+    <t>This is generally not the same as the Resource.text of the referenced resource.  The purpose is to identify what's being referenced, not to fully describe it.</t>
+  </si>
+  <si>
+    <t>Reference.display</t>
   </si>
   <si>
     <t>Observation.focus</t>
@@ -725,6 +866,9 @@
     <t>Typically, an observation is made about the subject - a patient, or group of patients, location, or device - and the distinction between the subject and what is directly measured for an observation is specified in the observation code itself ( e.g., "Blood Glucose") and does not need to be represented separately using this element.  Use `specimen` if a reference to a specimen is required.  If a code is required instead of a resource use either  `bodysite` for bodysites or the standard extension [focusCode](http://hl7.org/fhir/R4/extension-observation-focuscode.html).</t>
   </si>
   <si>
+    <t>OBX-3</t>
+  </si>
+  <si>
     <t>participation[typeCode=SBJ]</t>
   </si>
   <si>
@@ -771,7 +915,7 @@
   </si>
   <si>
     <t>dateTime
-PeriodTiminginstant</t>
+Period</t>
   </si>
   <si>
     <t>Clinically relevant time/time-period for observation</t>
@@ -796,6 +940,31 @@
   </si>
   <si>
     <t>FiveWs.done[x]</t>
+  </si>
+  <si>
+    <t>Observation.effective[x].id</t>
+  </si>
+  <si>
+    <t>Observation.effective[x].extension</t>
+  </si>
+  <si>
+    <t>Observation.effective[x].extension:data-absent-reason</t>
+  </si>
+  <si>
+    <t>data-absent-reason</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {data-absent-reason}
+</t>
+  </si>
+  <si>
+    <t>effective[x] absence reason</t>
+  </si>
+  <si>
+    <t>Provides a reason why the effectiveTime is missing.</t>
+  </si>
+  <si>
+    <t>ANY.nullFlavor</t>
   </si>
   <si>
     <t>Observation.issued</t>
@@ -854,10 +1023,6 @@
     <t>Observation.value[x]</t>
   </si>
   <si>
-    <t>Quantity
-CodeableConceptstringbooleanintegerRangeRatioSampledDatatimedateTimePeriod</t>
-  </si>
-  <si>
     <t>Actual result</t>
   </si>
   <si>
@@ -874,7 +1039,7 @@
 </t>
   </si>
   <si>
-    <t>open</t>
+    <t>closed</t>
   </si>
   <si>
     <t xml:space="preserve">obs-7
@@ -899,7 +1064,29 @@
     <t>valueCodeableConcept</t>
   </si>
   <si>
+    <t>A concept that may be defined by a formal reference to a terminology or ontology or may be provided by text.</t>
+  </si>
+  <si>
+    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
+  </si>
+  <si>
     <t>http://hl7.org/fhir/uv/ips/ValueSet/results-coded-values-laboratory-pathology-uv-ips</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueString</t>
+  </si>
+  <si>
+    <t>valueString</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueQuantity</t>
+  </si>
+  <si>
+    <t>valueQuantity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantity
+</t>
   </si>
   <si>
     <t>Observation.dataAbsentReason</t>
@@ -938,31 +1125,10 @@
 </t>
   </si>
   <si>
-    <t>High, low, normal, etc.</t>
-  </si>
-  <si>
-    <t>A categorical assessment of an observation value.  For example, high, low, normal.</t>
-  </si>
-  <si>
-    <t>Historically used for laboratory results (known as 'abnormal flag' ),  its use extends to other use cases where coded interpretations  are relevant.  Often reported as one or more simple compact codes this element is often placed adjacent to the result value in reports and flow sheets to signal the meaning/normalcy status of the result.</t>
-  </si>
-  <si>
     <t>For some results, particularly numeric results, an interpretation is necessary to fully understand the significance of a result.</t>
   </si>
   <si>
-    <t>https://termgit.elga.gv.at/ValueSet/elga-observationinterpretation</t>
-  </si>
-  <si>
-    <t>&lt; 260245000 |Findings values|</t>
-  </si>
-  <si>
-    <t>OBX-8</t>
-  </si>
-  <si>
-    <t>interpretationCode</t>
-  </si>
-  <si>
-    <t>363713009 |Has interpretation|</t>
+    <t>https://fhir.hl7.at/elga-austrianpatientsummary-r4/ValueSet/at-aps-observationinterpretation</t>
   </si>
   <si>
     <t>Observation.note</t>
@@ -1139,29 +1305,7 @@
     <t>Observation.referenceRange.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>Observation.referenceRange.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>Observation.referenceRange.modifierExtension</t>
@@ -1249,6 +1393,9 @@
     <t>OBX-10</t>
   </si>
   <si>
+    <t>interpretationCode</t>
+  </si>
+  <si>
     <t>Observation.referenceRange.appliesTo</t>
   </si>
   <si>
@@ -1311,10 +1458,10 @@
     <t>Related resource that belongs to the Observation group</t>
   </si>
   <si>
-    <t>This observation is a group observation (e.g. a battery, a panel of tests, a set of vital sign measurements) that includes the target as a member of the group.</t>
-  </si>
-  <si>
-    <t>When using this element, an observation will typically have either a value or a set of related resources, although both may be present in some cases.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.  Note that a system may calculate results from [QuestionnaireResponse](http://hl7.org/fhir/R4/questionnaireresponse.html)  into a final score and represent the score as an Observation.</t>
+    <t>A reference to another Observation profiled by Observation-results-laboratory-pathology-uv-ips. The target observation (for instance an individual test member of a panel) is considered as a sub-observation of the current one, which plays the role of a grouper.</t>
+  </si>
+  <si>
+    <t>This element is used in the context of international patient summary when there is a need to group a collection of observations, because they belong to the same panel, or because they share a common interpretation comment, or a common media attachment (illustrative image or graph). In these cases, the current observation is the grouper, and its set of sub-observations are related observations using the type "has-member".  For a discussion on the ways Observations can be assembled in groups together see [Observation Grouping](http://hl7.org/fhir/observation.html#obsgrouping).</t>
   </si>
   <si>
     <t>Relationships established by OBX-4 usage</t>
@@ -1384,19 +1531,23 @@
     <t>*All* code-value and  component.code-component.value pairs need to be taken into account to correctly understand the meaning of the observation.</t>
   </si>
   <si>
-    <t>Codes identifying names of simple observations.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
-  </si>
-  <si>
     <t>&lt; 363787002 |Observable entity| OR  &lt; 386053000 |Evaluation procedure|</t>
   </si>
   <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>FiveWs.what[x]</t>
+  </si>
+  <si>
     <t>Observation.component.value[x]</t>
   </si>
   <si>
+    <t>Quantity
+CodeableConceptstringbooleanintegerRangeRatioSampledDatatimedateTimePeriod</t>
+  </si>
+  <si>
     <t>Actual component result</t>
   </si>
   <si>
@@ -1404,6 +1555,9 @@
   </si>
   <si>
     <t>363714003 |Interprets| &lt; 441742003 |Evaluation finding|</t>
+  </si>
+  <si>
+    <t>Observation.component.value[x]:valueCodeableConcept</t>
   </si>
   <si>
     <t>Observation.component.dataAbsentReason</t>
@@ -1422,10 +1576,22 @@
     <t>Observation.component.interpretation</t>
   </si>
   <si>
-    <t>Codes identifying interpretations of observations.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
+    <t>High, low, normal, etc.</t>
+  </si>
+  <si>
+    <t>A categorical assessment of an observation value.  For example, high, low, normal.</t>
+  </si>
+  <si>
+    <t>Historically used for laboratory results (known as 'abnormal flag' ),  its use extends to other use cases where coded interpretations  are relevant.  Often reported as one or more simple compact codes this element is often placed adjacent to the result value in reports and flow sheets to signal the meaning/normalcy status of the result.</t>
+  </si>
+  <si>
+    <t>&lt; 260245000 |Findings values|</t>
+  </si>
+  <si>
+    <t>OBX-8</t>
+  </si>
+  <si>
+    <t>363713009 |Has interpretation|</t>
   </si>
   <si>
     <t>Observation.component.referenceRange</t>
@@ -1563,6 +1729,21 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color indexed="22"/>
+        <i val="true"/>
+      </font>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -1736,14 +1917,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP52"/>
+  <dimension ref="A1:AP65"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="44.67578125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="53.09375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="44.67578125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="22.25390625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="34.5390625" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
@@ -1764,10 +1945,10 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="63.70703125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="77.55859375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="86.34375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="41.01953125" customWidth="true" bestFit="true" hidden="true"/>
@@ -1910,7 +2091,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
         <v>30</v>
       </c>
@@ -2030,7 +2211,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
         <v>91</v>
       </c>
@@ -2150,7 +2331,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
         <v>99</v>
       </c>
@@ -2268,7 +2449,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
         <v>105</v>
       </c>
@@ -2388,7 +2569,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
         <v>111</v>
       </c>
@@ -2508,7 +2689,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
         <v>120</v>
       </c>
@@ -2628,7 +2809,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
         <v>128</v>
       </c>
@@ -2748,7 +2929,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
         <v>136</v>
       </c>
@@ -2868,7 +3049,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
         <v>144</v>
       </c>
@@ -2990,7 +3171,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
         <v>149</v>
       </c>
@@ -3110,7 +3291,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
         <v>158</v>
       </c>
@@ -3230,7 +3411,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
         <v>167</v>
       </c>
@@ -3350,7 +3531,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
         <v>176</v>
       </c>
@@ -3361,7 +3542,9 @@
       <c r="D14" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="E14" s="2"/>
+      <c r="E14" t="s" s="2">
+        <v>177</v>
+      </c>
       <c r="F14" t="s" s="2">
         <v>92</v>
       </c>
@@ -3381,16 +3564,16 @@
         <v>112</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>82</v>
@@ -3415,11 +3598,9 @@
         <v>82</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="Y14" t="s" s="2">
         <v>182</v>
       </c>
+      <c r="Y14" s="2"/>
       <c r="Z14" t="s" s="2">
         <v>183</v>
       </c>
@@ -3472,7 +3653,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
         <v>189</v>
       </c>
@@ -3485,7 +3666,7 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G15" t="s" s="2">
         <v>81</v>
@@ -3547,16 +3728,14 @@
         <v>82</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="AC15" s="2"/>
       <c r="AD15" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>82</v>
+        <v>198</v>
       </c>
       <c r="AF15" t="s" s="2">
         <v>189</v>
@@ -3583,25 +3762,27 @@
         <v>82</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="C16" s="2"/>
+        <v>189</v>
+      </c>
+      <c r="C16" t="s" s="2">
+        <v>202</v>
+      </c>
       <c r="D16" t="s" s="2">
-        <v>200</v>
+        <v>82</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3611,28 +3792,28 @@
         <v>92</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>82</v>
@@ -3642,7 +3823,7 @@
         <v>82</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>82</v>
+        <v>206</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>82</v>
@@ -3657,11 +3838,13 @@
         <v>82</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="Y16" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="Y16" t="s" s="2">
+        <v>207</v>
+      </c>
       <c r="Z16" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>82</v>
@@ -3679,13 +3862,13 @@
         <v>82</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>82</v>
@@ -3694,65 +3877,65 @@
         <v>104</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>207</v>
+        <v>82</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>208</v>
+        <v>82</v>
       </c>
       <c r="AM16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN16" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AO16" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="AP16" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="17" hidden="true">
+      <c r="A17" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="AN16" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="AO16" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="AP16" t="s" s="2">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s" s="2">
-        <v>213</v>
-      </c>
       <c r="B17" t="s" s="2">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>82</v>
+        <v>210</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>92</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="L17" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="M17" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="N17" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="O17" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="L17" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>218</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>82</v>
@@ -3777,13 +3960,11 @@
         <v>82</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y17" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="Y17" s="2"/>
       <c r="Z17" t="s" s="2">
-        <v>82</v>
+        <v>215</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>82</v>
@@ -3801,45 +3982,45 @@
         <v>82</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="AH17" t="s" s="2">
         <v>92</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>82</v>
+        <v>216</v>
       </c>
       <c r="AJ17" t="s" s="2">
         <v>104</v>
       </c>
       <c r="AK17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM17" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="AN17" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="AO17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP17" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="18" hidden="true">
+      <c r="A18" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="AL17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM17" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="AN17" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="AO17" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="AP17" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s" s="2">
-        <v>223</v>
-      </c>
       <c r="B18" t="s" s="2">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3847,13 +4028,13 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>82</v>
@@ -3862,18 +4043,20 @@
         <v>93</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="L18" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="M18" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="O18" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="L18" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>82</v>
       </c>
@@ -3921,13 +4104,13 @@
         <v>82</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>82</v>
@@ -3936,25 +4119,25 @@
         <v>104</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>82</v>
+        <v>225</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>209</v>
+        <v>226</v>
       </c>
       <c r="AN18" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="AO18" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="AO18" t="s" s="2">
-        <v>222</v>
-      </c>
       <c r="AP18" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
         <v>229</v>
       </c>
@@ -3963,7 +4146,7 @@
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>230</v>
+        <v>82</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3979,23 +4162,19 @@
         <v>82</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="M19" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>235</v>
-      </c>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>82</v>
       </c>
@@ -4043,7 +4222,7 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4055,44 +4234,44 @@
         <v>82</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>236</v>
+        <v>82</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>237</v>
+        <v>82</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>239</v>
+        <v>82</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>241</v>
+        <v>137</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>82</v>
@@ -4101,23 +4280,21 @@
         <v>82</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>242</v>
+        <v>138</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>243</v>
+        <v>139</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>246</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>82</v>
       </c>
@@ -4153,57 +4330,57 @@
         <v>82</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>82</v>
+        <v>237</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>82</v>
+        <v>238</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>82</v>
+        <v>198</v>
       </c>
       <c r="AF20" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="AG20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH20" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ20" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="AK20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN20" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="AO20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP20" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="21" hidden="true">
+      <c r="A21" t="s" s="2">
         <v>240</v>
       </c>
-      <c r="AG20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH20" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ20" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK20" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="AL20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM20" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="AN20" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="AO20" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="AP20" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s" s="2">
-        <v>251</v>
-      </c>
       <c r="B21" t="s" s="2">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4211,13 +4388,13 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>92</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>82</v>
@@ -4226,16 +4403,16 @@
         <v>93</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4285,7 +4462,7 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4294,7 +4471,7 @@
         <v>92</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>82</v>
+        <v>245</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>104</v>
@@ -4306,24 +4483,24 @@
         <v>82</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>256</v>
+        <v>82</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>257</v>
+        <v>135</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>258</v>
+        <v>82</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>259</v>
+        <v>246</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>259</v>
+        <v>246</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4334,7 +4511,7 @@
         <v>80</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>82</v>
@@ -4346,18 +4523,18 @@
         <v>93</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>260</v>
+        <v>106</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>261</v>
+        <v>247</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="N22" s="2"/>
-      <c r="O22" t="s" s="2">
-        <v>263</v>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>82</v>
       </c>
@@ -4381,13 +4558,13 @@
         <v>82</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>82</v>
+        <v>195</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>82</v>
+        <v>250</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>82</v>
+        <v>251</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>82</v>
@@ -4405,13 +4582,13 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>82</v>
@@ -4420,30 +4597,30 @@
         <v>104</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>264</v>
+        <v>82</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>265</v>
+        <v>82</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>266</v>
+        <v>135</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>267</v>
+        <v>82</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>268</v>
+        <v>253</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>268</v>
+        <v>253</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4466,20 +4643,18 @@
         <v>93</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>269</v>
+        <v>150</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>270</v>
+        <v>254</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>271</v>
+        <v>255</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>273</v>
-      </c>
+        <v>256</v>
+      </c>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>82</v>
       </c>
@@ -4515,17 +4690,19 @@
         <v>82</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="AC23" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC23" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>275</v>
+        <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4534,7 +4711,7 @@
         <v>92</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>276</v>
+        <v>82</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>104</v>
@@ -4543,31 +4720,29 @@
         <v>82</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>277</v>
+        <v>82</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>278</v>
+        <v>82</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>279</v>
+        <v>258</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>280</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>281</v>
+        <v>259</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="C24" t="s" s="2">
-        <v>282</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
         <v>82</v>
       </c>
@@ -4588,20 +4763,18 @@
         <v>93</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>190</v>
+        <v>230</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>273</v>
-      </c>
+        <v>262</v>
+      </c>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>82</v>
       </c>
@@ -4625,11 +4798,13 @@
         <v>82</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="Y24" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y24" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z24" t="s" s="2">
-        <v>283</v>
+        <v>82</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>82</v>
@@ -4647,7 +4822,7 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4656,7 +4831,7 @@
         <v>92</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>276</v>
+        <v>82</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>104</v>
@@ -4665,27 +4840,27 @@
         <v>82</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>277</v>
+        <v>82</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>278</v>
+        <v>82</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>279</v>
+        <v>135</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>280</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>284</v>
+        <v>264</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>284</v>
+        <v>264</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4696,7 +4871,7 @@
         <v>80</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>82</v>
@@ -4705,23 +4880,21 @@
         <v>82</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>190</v>
+        <v>265</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>285</v>
+        <v>266</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>286</v>
+        <v>267</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>288</v>
-      </c>
+        <v>268</v>
+      </c>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>82</v>
       </c>
@@ -4745,13 +4918,13 @@
         <v>82</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>195</v>
+        <v>82</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>289</v>
+        <v>82</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>290</v>
+        <v>82</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>82</v>
@@ -4769,16 +4942,16 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>284</v>
+        <v>264</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>291</v>
+        <v>82</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>104</v>
@@ -4790,35 +4963,35 @@
         <v>82</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>135</v>
+        <v>269</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>292</v>
+        <v>270</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>82</v>
+        <v>228</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>293</v>
+        <v>271</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>293</v>
+        <v>271</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>294</v>
+        <v>272</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>82</v>
@@ -4827,22 +5000,22 @@
         <v>82</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>190</v>
+        <v>273</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>295</v>
+        <v>274</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>296</v>
+        <v>275</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>297</v>
+        <v>276</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>298</v>
+        <v>277</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
@@ -4867,11 +5040,13 @@
         <v>82</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="Y26" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z26" t="s" s="2">
-        <v>299</v>
+        <v>82</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>82</v>
@@ -4889,13 +5064,13 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>293</v>
+        <v>271</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>82</v>
@@ -4904,65 +5079,65 @@
         <v>104</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>82</v>
+        <v>278</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>300</v>
+        <v>82</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>301</v>
+        <v>279</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>302</v>
+        <v>280</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>82</v>
+        <v>281</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>303</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>304</v>
+        <v>282</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>304</v>
+        <v>282</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>82</v>
+        <v>283</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>305</v>
+        <v>284</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>306</v>
+        <v>285</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>307</v>
+        <v>286</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>308</v>
+        <v>287</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>309</v>
+        <v>288</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>82</v>
@@ -5011,13 +5186,13 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>304</v>
+        <v>282</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>82</v>
@@ -5026,30 +5201,30 @@
         <v>104</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>82</v>
+        <v>289</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>310</v>
+        <v>290</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>311</v>
+        <v>291</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>82</v>
+        <v>292</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>312</v>
+        <v>293</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>312</v>
+        <v>293</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5072,17 +5247,15 @@
         <v>82</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>190</v>
+        <v>230</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>313</v>
+        <v>231</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>315</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>82</v>
@@ -5107,13 +5280,13 @@
         <v>82</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>316</v>
+        <v>82</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>317</v>
+        <v>82</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>318</v>
+        <v>82</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>82</v>
@@ -5131,7 +5304,7 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>312</v>
+        <v>233</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5143,44 +5316,44 @@
         <v>82</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>319</v>
+        <v>82</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>320</v>
+        <v>82</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>321</v>
+        <v>234</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>322</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>323</v>
+        <v>294</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>323</v>
+        <v>294</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>82</v>
+        <v>137</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>82</v>
@@ -5192,20 +5365,18 @@
         <v>82</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>190</v>
+        <v>138</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>324</v>
+        <v>139</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>325</v>
+        <v>236</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>327</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>82</v>
       </c>
@@ -5229,43 +5400,43 @@
         <v>82</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>316</v>
+        <v>82</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>328</v>
+        <v>82</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>329</v>
+        <v>82</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>82</v>
+        <v>237</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>82</v>
+        <v>238</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>82</v>
+        <v>198</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>323</v>
+        <v>239</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>82</v>
@@ -5274,10 +5445,10 @@
         <v>82</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>330</v>
+        <v>82</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>331</v>
+        <v>234</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>82</v>
@@ -5286,14 +5457,16 @@
         <v>82</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>332</v>
+        <v>295</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="C30" s="2"/>
+        <v>294</v>
+      </c>
+      <c r="C30" t="s" s="2">
+        <v>296</v>
+      </c>
       <c r="D30" t="s" s="2">
         <v>82</v>
       </c>
@@ -5305,7 +5478,7 @@
         <v>92</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>82</v>
@@ -5314,17 +5487,15 @@
         <v>82</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>333</v>
+        <v>297</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>334</v>
+        <v>298</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>336</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>82</v>
@@ -5373,45 +5544,45 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>332</v>
+        <v>239</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>337</v>
+        <v>82</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>338</v>
+        <v>82</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>339</v>
+        <v>300</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>340</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>341</v>
+        <v>301</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>341</v>
+        <v>301</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5431,19 +5602,19 @@
         <v>82</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>342</v>
+        <v>302</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>343</v>
+        <v>303</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>344</v>
+        <v>304</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>345</v>
+        <v>305</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5493,7 +5664,7 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>341</v>
+        <v>301</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5511,27 +5682,27 @@
         <v>82</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>346</v>
+        <v>82</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>347</v>
+        <v>306</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>348</v>
+        <v>307</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>82</v>
+        <v>308</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>349</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>350</v>
+        <v>309</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>350</v>
+        <v>309</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5539,34 +5710,32 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>81</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>351</v>
+        <v>310</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>352</v>
+        <v>311</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>354</v>
-      </c>
+        <v>312</v>
+      </c>
+      <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
-        <v>355</v>
+        <v>313</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>82</v>
@@ -5615,7 +5784,7 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>350</v>
+        <v>309</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5627,33 +5796,33 @@
         <v>82</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>356</v>
+        <v>104</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>82</v>
+        <v>314</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>357</v>
+        <v>315</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>358</v>
+        <v>316</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>82</v>
+        <v>317</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>359</v>
+        <v>318</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>359</v>
+        <v>318</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5673,19 +5842,23 @@
         <v>82</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>360</v>
+        <v>203</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>361</v>
+        <v>319</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="N33" s="2"/>
-      <c r="O33" s="2"/>
+        <v>320</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="O33" t="s" s="2">
+        <v>322</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>82</v>
       </c>
@@ -5721,19 +5894,17 @@
         <v>82</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC33" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>323</v>
+      </c>
+      <c r="AC33" s="2"/>
       <c r="AD33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>82</v>
+        <v>324</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>363</v>
+        <v>318</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5742,50 +5913,52 @@
         <v>92</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>82</v>
+        <v>325</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>82</v>
+        <v>326</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>82</v>
+        <v>327</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>364</v>
+        <v>328</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>82</v>
+        <v>329</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>365</v>
+        <v>330</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="C34" s="2"/>
+        <v>318</v>
+      </c>
+      <c r="C34" t="s" s="2">
+        <v>331</v>
+      </c>
       <c r="D34" t="s" s="2">
-        <v>137</v>
+        <v>82</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>82</v>
@@ -5794,18 +5967,20 @@
         <v>82</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>138</v>
+        <v>190</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>139</v>
+        <v>211</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>366</v>
+        <v>332</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="O34" s="2"/>
+        <v>333</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>322</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
       </c>
@@ -5829,13 +6004,11 @@
         <v>82</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y34" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="Y34" s="2"/>
       <c r="Z34" t="s" s="2">
-        <v>82</v>
+        <v>334</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>82</v>
@@ -5853,19 +6026,19 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>367</v>
+        <v>318</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>82</v>
+        <v>216</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>143</v>
+        <v>104</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>82</v>
@@ -5874,10 +6047,10 @@
         <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>82</v>
+        <v>217</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>364</v>
+        <v>218</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>82</v>
@@ -5886,47 +6059,49 @@
         <v>82</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>368</v>
+        <v>335</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="C35" s="2"/>
+        <v>318</v>
+      </c>
+      <c r="C35" t="s" s="2">
+        <v>336</v>
+      </c>
       <c r="D35" t="s" s="2">
-        <v>369</v>
+        <v>82</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="J35" t="s" s="2">
         <v>93</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>138</v>
+        <v>230</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>370</v>
+        <v>319</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>371</v>
+        <v>320</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>141</v>
+        <v>321</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>147</v>
+        <v>322</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
@@ -5975,47 +6150,49 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>372</v>
+        <v>318</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>82</v>
+        <v>325</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>143</v>
+        <v>104</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>82</v>
+        <v>326</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>82</v>
+        <v>327</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>135</v>
+        <v>328</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>82</v>
+        <v>329</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>373</v>
+        <v>337</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="C36" s="2"/>
+        <v>318</v>
+      </c>
+      <c r="C36" t="s" s="2">
+        <v>338</v>
+      </c>
       <c r="D36" t="s" s="2">
         <v>82</v>
       </c>
@@ -6027,25 +6204,29 @@
         <v>92</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>374</v>
+        <v>339</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>375</v>
+        <v>319</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="N36" s="2"/>
-      <c r="O36" s="2"/>
+        <v>320</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="O36" t="s" s="2">
+        <v>322</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>82</v>
       </c>
@@ -6093,7 +6274,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>373</v>
+        <v>318</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6102,7 +6283,7 @@
         <v>92</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>377</v>
+        <v>325</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>104</v>
@@ -6111,27 +6292,27 @@
         <v>82</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>82</v>
+        <v>326</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>378</v>
+        <v>327</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>379</v>
+        <v>328</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>82</v>
+        <v>329</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>380</v>
+        <v>340</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>380</v>
+        <v>340</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6154,16 +6335,20 @@
         <v>82</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>374</v>
+        <v>203</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>381</v>
+        <v>341</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="N37" s="2"/>
-      <c r="O37" s="2"/>
+        <v>342</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>344</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>82</v>
       </c>
@@ -6187,13 +6372,13 @@
         <v>82</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>82</v>
+        <v>195</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>82</v>
+        <v>345</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>82</v>
+        <v>346</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>82</v>
@@ -6211,7 +6396,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>380</v>
+        <v>340</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6220,7 +6405,7 @@
         <v>92</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>377</v>
+        <v>347</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>104</v>
@@ -6232,10 +6417,10 @@
         <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>378</v>
+        <v>135</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>383</v>
+        <v>348</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>82</v>
@@ -6244,23 +6429,23 @@
         <v>82</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>384</v>
+        <v>349</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>384</v>
+        <v>349</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>82</v>
+        <v>350</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>82</v>
@@ -6275,16 +6460,16 @@
         <v>190</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>385</v>
+        <v>211</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>386</v>
+        <v>332</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>387</v>
+        <v>333</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>388</v>
+        <v>351</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>82</v>
@@ -6309,13 +6494,11 @@
         <v>82</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="Y38" t="s" s="2">
-        <v>389</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="Y38" s="2"/>
       <c r="Z38" t="s" s="2">
-        <v>390</v>
+        <v>352</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>82</v>
@@ -6333,16 +6516,16 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>384</v>
+        <v>349</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>82</v>
+        <v>216</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>104</v>
@@ -6351,13 +6534,13 @@
         <v>82</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>391</v>
+        <v>82</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>392</v>
+        <v>217</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>302</v>
+        <v>218</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>82</v>
@@ -6366,12 +6549,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>393</v>
+        <v>353</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>393</v>
+        <v>353</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6394,19 +6577,19 @@
         <v>82</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>190</v>
+        <v>354</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>394</v>
+        <v>355</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>395</v>
+        <v>356</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>396</v>
+        <v>357</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>397</v>
+        <v>358</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -6431,13 +6614,13 @@
         <v>82</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>316</v>
+        <v>82</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>398</v>
+        <v>82</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>399</v>
+        <v>82</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>82</v>
@@ -6455,7 +6638,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>393</v>
+        <v>353</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6473,13 +6656,13 @@
         <v>82</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>391</v>
+        <v>82</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>392</v>
+        <v>359</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>302</v>
+        <v>360</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -6488,12 +6671,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>400</v>
+        <v>361</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>400</v>
+        <v>361</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6516,18 +6699,18 @@
         <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>401</v>
+        <v>203</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>402</v>
+        <v>362</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="N40" s="2"/>
-      <c r="O40" t="s" s="2">
-        <v>404</v>
-      </c>
+        <v>363</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>82</v>
       </c>
@@ -6551,13 +6734,13 @@
         <v>82</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>82</v>
+        <v>365</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>82</v>
+        <v>366</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>82</v>
+        <v>367</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>82</v>
@@ -6575,7 +6758,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>400</v>
+        <v>361</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6593,27 +6776,27 @@
         <v>82</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>82</v>
+        <v>368</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>82</v>
+        <v>369</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>405</v>
+        <v>370</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>82</v>
+        <v>371</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>406</v>
+        <v>372</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>406</v>
+        <v>372</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6636,16 +6819,20 @@
         <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>360</v>
+        <v>203</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>407</v>
+        <v>373</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="N41" s="2"/>
-      <c r="O41" s="2"/>
+        <v>374</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>376</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>82</v>
       </c>
@@ -6669,13 +6856,13 @@
         <v>82</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>82</v>
+        <v>365</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>82</v>
+        <v>377</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>82</v>
+        <v>378</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>82</v>
@@ -6693,7 +6880,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>406</v>
+        <v>372</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6714,10 +6901,10 @@
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>409</v>
+        <v>380</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -6726,12 +6913,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>410</v>
+        <v>381</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>410</v>
+        <v>381</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6742,7 +6929,7 @@
         <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>82</v>
@@ -6751,19 +6938,19 @@
         <v>82</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>411</v>
+        <v>382</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>412</v>
+        <v>383</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>413</v>
+        <v>384</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>414</v>
+        <v>385</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6813,13 +7000,13 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>410</v>
+        <v>381</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>82</v>
@@ -6831,27 +7018,27 @@
         <v>82</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>82</v>
+        <v>386</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>415</v>
+        <v>387</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>416</v>
+        <v>388</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>82</v>
+        <v>389</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>417</v>
+        <v>390</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>417</v>
+        <v>390</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6862,7 +7049,7 @@
         <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>82</v>
@@ -6871,19 +7058,19 @@
         <v>82</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>418</v>
+        <v>391</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>419</v>
+        <v>392</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>420</v>
+        <v>393</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>421</v>
+        <v>394</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6933,13 +7120,13 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>417</v>
+        <v>390</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>82</v>
@@ -6951,27 +7138,27 @@
         <v>82</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>82</v>
+        <v>395</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>415</v>
+        <v>396</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>422</v>
+        <v>397</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>82</v>
+        <v>398</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>423</v>
+        <v>399</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>423</v>
+        <v>399</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6991,22 +7178,22 @@
         <v>82</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>351</v>
+        <v>400</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>424</v>
+        <v>401</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>425</v>
+        <v>402</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>426</v>
+        <v>403</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>427</v>
+        <v>404</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
@@ -7055,7 +7242,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>423</v>
+        <v>399</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7067,7 +7254,7 @@
         <v>82</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>104</v>
+        <v>405</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>82</v>
@@ -7076,10 +7263,10 @@
         <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>428</v>
+        <v>406</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>429</v>
+        <v>407</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
@@ -7088,12 +7275,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>430</v>
+        <v>408</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>430</v>
+        <v>408</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7116,13 +7303,13 @@
         <v>82</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>360</v>
+        <v>230</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>361</v>
+        <v>231</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>362</v>
+        <v>232</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7173,7 +7360,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>363</v>
+        <v>233</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7197,7 +7384,7 @@
         <v>82</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>364</v>
+        <v>234</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>82</v>
@@ -7206,12 +7393,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>431</v>
+        <v>409</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>431</v>
+        <v>409</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7240,7 +7427,7 @@
         <v>139</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>366</v>
+        <v>236</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>141</v>
@@ -7293,7 +7480,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>367</v>
+        <v>239</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7317,7 +7504,7 @@
         <v>82</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>364</v>
+        <v>234</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>82</v>
@@ -7326,16 +7513,16 @@
         <v>82</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>432</v>
+        <v>410</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>432</v>
+        <v>410</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>369</v>
+        <v>411</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7357,10 +7544,10 @@
         <v>138</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>370</v>
+        <v>412</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>371</v>
+        <v>413</v>
       </c>
       <c r="N47" t="s" s="2">
         <v>141</v>
@@ -7415,7 +7602,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>372</v>
+        <v>414</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7448,12 +7635,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>433</v>
+        <v>415</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>433</v>
+        <v>415</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7461,7 +7648,7 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>92</v>
@@ -7473,23 +7660,19 @@
         <v>82</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>190</v>
+        <v>416</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>434</v>
+        <v>417</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>205</v>
-      </c>
+        <v>418</v>
+      </c>
+      <c r="N48" s="2"/>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>82</v>
       </c>
@@ -7513,13 +7696,13 @@
         <v>82</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>316</v>
+        <v>82</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>437</v>
+        <v>82</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>438</v>
+        <v>82</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>82</v>
@@ -7537,16 +7720,16 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>433</v>
+        <v>415</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="AH48" t="s" s="2">
         <v>92</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>82</v>
+        <v>419</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>104</v>
@@ -7555,27 +7738,27 @@
         <v>82</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>439</v>
+        <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>209</v>
+        <v>420</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>210</v>
+        <v>421</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>211</v>
+        <v>82</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>440</v>
+        <v>422</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>440</v>
+        <v>422</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7595,23 +7778,19 @@
         <v>82</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>269</v>
+        <v>416</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>441</v>
+        <v>423</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>273</v>
-      </c>
+        <v>424</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>82</v>
       </c>
@@ -7659,7 +7838,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>440</v>
+        <v>422</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7668,7 +7847,7 @@
         <v>92</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>82</v>
+        <v>419</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>104</v>
@@ -7677,27 +7856,27 @@
         <v>82</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>443</v>
+        <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>278</v>
+        <v>420</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>279</v>
+        <v>425</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>280</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>444</v>
+        <v>426</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>444</v>
+        <v>426</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7720,19 +7899,19 @@
         <v>82</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>445</v>
+        <v>427</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>446</v>
+        <v>428</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>447</v>
+        <v>429</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>288</v>
+        <v>430</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -7757,13 +7936,13 @@
         <v>82</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>195</v>
+        <v>116</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>289</v>
+        <v>431</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>290</v>
+        <v>432</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>82</v>
@@ -7781,7 +7960,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>444</v>
+        <v>426</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7790,7 +7969,7 @@
         <v>92</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>291</v>
+        <v>82</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>104</v>
@@ -7799,13 +7978,13 @@
         <v>82</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>82</v>
+        <v>433</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>135</v>
+        <v>434</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>292</v>
+        <v>435</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -7814,16 +7993,16 @@
         <v>82</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>448</v>
+        <v>436</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>448</v>
+        <v>436</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>294</v>
+        <v>82</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7842,19 +8021,19 @@
         <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>295</v>
+        <v>437</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>296</v>
+        <v>438</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>297</v>
+        <v>439</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>298</v>
+        <v>440</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -7879,13 +8058,13 @@
         <v>82</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>195</v>
+        <v>365</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>449</v>
+        <v>441</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>450</v>
+        <v>442</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>82</v>
@@ -7903,7 +8082,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>448</v>
+        <v>436</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -7921,27 +8100,27 @@
         <v>82</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>300</v>
+        <v>433</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>301</v>
+        <v>434</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>302</v>
+        <v>435</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>303</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>451</v>
+        <v>443</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>451</v>
+        <v>443</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7952,7 +8131,7 @@
         <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>82</v>
@@ -7964,19 +8143,17 @@
         <v>82</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>83</v>
+        <v>444</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>452</v>
+        <v>445</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>354</v>
-      </c>
+        <v>446</v>
+      </c>
+      <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>355</v>
+        <v>447</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
@@ -8025,13 +8202,13 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>451</v>
+        <v>443</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>82</v>
@@ -8046,19 +8223,1603 @@
         <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>357</v>
+        <v>82</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>358</v>
+        <v>448</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP52" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="53" hidden="true">
+      <c r="A53" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E53" s="2"/>
+      <c r="F53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G53" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K53" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="N53" s="2"/>
+      <c r="O53" s="2"/>
+      <c r="P53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q53" s="2"/>
+      <c r="R53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF53" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="AG53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH53" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="AN53" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="AO53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP53" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="54" hidden="true">
+      <c r="A54" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E54" s="2"/>
+      <c r="F54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J54" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="K54" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="O54" s="2"/>
+      <c r="P54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q54" s="2"/>
+      <c r="R54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF54" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="AG54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="AN54" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AO54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP54" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="55" hidden="true">
+      <c r="A55" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E55" s="2"/>
+      <c r="F55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J55" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="K55" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="O55" s="2"/>
+      <c r="P55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q55" s="2"/>
+      <c r="R55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF55" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="AG55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="AN55" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AO55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP55" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="56" hidden="true">
+      <c r="A56" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E56" s="2"/>
+      <c r="F56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H56" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J56" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="K56" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="P56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q56" s="2"/>
+      <c r="R56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF56" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="AN56" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="AO56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP56" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="57" hidden="true">
+      <c r="A57" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E57" s="2"/>
+      <c r="F57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K57" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="N57" s="2"/>
+      <c r="O57" s="2"/>
+      <c r="P57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q57" s="2"/>
+      <c r="R57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF57" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN57" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="AO57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP57" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="58" hidden="true">
+      <c r="A58" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="O58" s="2"/>
+      <c r="P58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q58" s="2"/>
+      <c r="R58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="AO58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP58" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="59" hidden="true">
+      <c r="A59" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="P59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q59" s="2"/>
+      <c r="R59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN59" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AO59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP59" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="60" hidden="true">
+      <c r="A60" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="P60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q60" s="2"/>
+      <c r="R60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="Y60" s="2"/>
+      <c r="Z60" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="AN60" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="AO60" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="AP60" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="61" hidden="true">
+      <c r="A61" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="P61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="AC61" s="2"/>
+      <c r="AD61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AO61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP61" t="s" s="2">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="62" hidden="true">
+      <c r="A62" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="C62" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="D62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="P62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="Y62" s="2"/>
+      <c r="Z62" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AO62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP62" t="s" s="2">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="63" hidden="true">
+      <c r="A63" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="P63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="AO63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP63" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="64" hidden="true">
+      <c r="A64" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="O64" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="P64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="Y64" s="2"/>
+      <c r="Z64" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="AO64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP64" t="s" s="2">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="65" hidden="true">
+      <c r="A65" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="P65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="AO65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP65" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AP65">
+    <filterColumn colId="6">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+    <filterColumn colId="26">
+      <filters blank="true"/>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="A2:AI64">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$G2&lt;&gt;"Y"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$Q2&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>